--- a/CORTES DE CAJA/2026/3)MARZO/LISTA DE VENTAS SEMANA 12 DE MARZO -26.xlsx
+++ b/CORTES DE CAJA/2026/3)MARZO/LISTA DE VENTAS SEMANA 12 DE MARZO -26.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F871D704-D0D9-4E62-B751-89585FF12FFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9558DD4-21A1-413F-B70F-7F7034904BBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lunes 16-03-26" sheetId="1" r:id="rId1"/>
@@ -807,7 +807,7 @@
     <t>CARGADO</t>
   </si>
   <si>
-    <t>CUENTA DE AYER $ 27511  MENOS $ 17526  
+    <t>CUENTA DE AYER $ 27511  MENOS $ 9985 QUEDA $ 17526
 CUENTA DE HOY SABADO $ 4762.5 MENOS $ 300 PAGO DE YAS QUEDA $ 4462.5  
 TOTAL EN CAJA $ 21998.5</t>
   </si>
@@ -1183,6 +1183,27 @@
     <xf numFmtId="164" fontId="0" fillId="7" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -1222,26 +1243,8 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1260,9 +1263,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1851,23 +1851,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="C2" s="35" t="s">
+      <c r="C2" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="35"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
       <c r="L2" s="8"/>
-      <c r="M2" s="35" t="s">
+      <c r="M2" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="36"/>
-      <c r="O2" s="36"/>
-      <c r="P2" s="36"/>
-      <c r="Q2" s="36"/>
-      <c r="R2" s="36"/>
+      <c r="N2" s="23"/>
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
+      <c r="R2" s="23"/>
     </row>
     <row r="3" spans="2:18" ht="26.25" x14ac:dyDescent="0.4">
       <c r="G3" t="s">
@@ -1880,14 +1880,14 @@
         <f>SUM(Tabla1[Importa])</f>
         <v>1383.5</v>
       </c>
-      <c r="M3" s="38" t="s">
+      <c r="M3" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="38"/>
-      <c r="O3" s="38"/>
-      <c r="P3" s="38"/>
-      <c r="Q3" s="38"/>
-      <c r="R3" s="38"/>
+      <c r="N3" s="25"/>
+      <c r="O3" s="25"/>
+      <c r="P3" s="25"/>
+      <c r="Q3" s="25"/>
+      <c r="R3" s="25"/>
     </row>
     <row r="4" spans="2:18" ht="31.5" x14ac:dyDescent="0.5">
       <c r="B4" s="17" t="s">
@@ -1918,19 +1918,19 @@
         <f>COUNTIF(C5:C103,"&gt;0")</f>
         <v>16</v>
       </c>
-      <c r="M4" s="37" t="s">
+      <c r="M4" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="N4" s="37"/>
-      <c r="O4" s="37"/>
-      <c r="P4" s="37"/>
-      <c r="Q4" s="37"/>
-      <c r="R4" s="37"/>
+      <c r="N4" s="24"/>
+      <c r="O4" s="24"/>
+      <c r="P4" s="24"/>
+      <c r="Q4" s="24"/>
+      <c r="R4" s="24"/>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B5" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C5">
         <f>IF(ISNUMBER(E5), IF(ISNUMBER(C4), C4+1, 1), "")</f>
@@ -1949,21 +1949,21 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G5))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>20</v>
       </c>
-      <c r="J5" s="39" t="s">
+      <c r="J5" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="K5" s="39"/>
-      <c r="M5" s="37"/>
-      <c r="N5" s="37"/>
-      <c r="O5" s="37"/>
-      <c r="P5" s="37"/>
-      <c r="Q5" s="37"/>
-      <c r="R5" s="37"/>
+      <c r="K5" s="26"/>
+      <c r="M5" s="24"/>
+      <c r="N5" s="24"/>
+      <c r="O5" s="24"/>
+      <c r="P5" s="24"/>
+      <c r="Q5" s="24"/>
+      <c r="R5" s="24"/>
     </row>
     <row r="6" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C6">
         <f t="shared" ref="C6:C36" si="0">IF(ISNUMBER(E6), IF(ISNUMBER(C5), C5+1, 1), "")</f>
@@ -1985,19 +1985,19 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G6))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>111.5</v>
       </c>
-      <c r="J6" s="39"/>
-      <c r="K6" s="39"/>
-      <c r="M6" s="37"/>
-      <c r="N6" s="37"/>
-      <c r="O6" s="37"/>
-      <c r="P6" s="37"/>
-      <c r="Q6" s="37"/>
-      <c r="R6" s="37"/>
+      <c r="J6" s="26"/>
+      <c r="K6" s="26"/>
+      <c r="M6" s="24"/>
+      <c r="N6" s="24"/>
+      <c r="O6" s="24"/>
+      <c r="P6" s="24"/>
+      <c r="Q6" s="24"/>
+      <c r="R6" s="24"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B7" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
@@ -2019,19 +2019,19 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G7))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>40.5</v>
       </c>
-      <c r="J7" s="39"/>
-      <c r="K7" s="39"/>
-      <c r="M7" s="37"/>
-      <c r="N7" s="37"/>
-      <c r="O7" s="37"/>
-      <c r="P7" s="37"/>
-      <c r="Q7" s="37"/>
-      <c r="R7" s="37"/>
+      <c r="J7" s="26"/>
+      <c r="K7" s="26"/>
+      <c r="M7" s="24"/>
+      <c r="N7" s="24"/>
+      <c r="O7" s="24"/>
+      <c r="P7" s="24"/>
+      <c r="Q7" s="24"/>
+      <c r="R7" s="24"/>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B8" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C8">
         <f t="shared" si="0"/>
@@ -2053,19 +2053,19 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G8))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>45</v>
       </c>
-      <c r="J8" s="39"/>
-      <c r="K8" s="39"/>
-      <c r="M8" s="37"/>
-      <c r="N8" s="37"/>
-      <c r="O8" s="37"/>
-      <c r="P8" s="37"/>
-      <c r="Q8" s="37"/>
-      <c r="R8" s="37"/>
+      <c r="J8" s="26"/>
+      <c r="K8" s="26"/>
+      <c r="M8" s="24"/>
+      <c r="N8" s="24"/>
+      <c r="O8" s="24"/>
+      <c r="P8" s="24"/>
+      <c r="Q8" s="24"/>
+      <c r="R8" s="24"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B9" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C9">
         <f t="shared" si="0"/>
@@ -2084,19 +2084,19 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G9))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>5</v>
       </c>
-      <c r="J9" s="39"/>
-      <c r="K9" s="39"/>
-      <c r="M9" s="37"/>
-      <c r="N9" s="37"/>
-      <c r="O9" s="37"/>
-      <c r="P9" s="37"/>
-      <c r="Q9" s="37"/>
-      <c r="R9" s="37"/>
+      <c r="J9" s="26"/>
+      <c r="K9" s="26"/>
+      <c r="M9" s="24"/>
+      <c r="N9" s="24"/>
+      <c r="O9" s="24"/>
+      <c r="P9" s="24"/>
+      <c r="Q9" s="24"/>
+      <c r="R9" s="24"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B10" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C10">
         <f t="shared" si="0"/>
@@ -2115,19 +2115,19 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G10))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>20</v>
       </c>
-      <c r="J10" s="39"/>
-      <c r="K10" s="39"/>
-      <c r="M10" s="37"/>
-      <c r="N10" s="37"/>
-      <c r="O10" s="37"/>
-      <c r="P10" s="37"/>
-      <c r="Q10" s="37"/>
-      <c r="R10" s="37"/>
+      <c r="J10" s="26"/>
+      <c r="K10" s="26"/>
+      <c r="M10" s="24"/>
+      <c r="N10" s="24"/>
+      <c r="O10" s="24"/>
+      <c r="P10" s="24"/>
+      <c r="Q10" s="24"/>
+      <c r="R10" s="24"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B11" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C11">
         <f t="shared" si="0"/>
@@ -2146,19 +2146,19 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G11))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>85</v>
       </c>
-      <c r="J11" s="39"/>
-      <c r="K11" s="39"/>
-      <c r="M11" s="37"/>
-      <c r="N11" s="37"/>
-      <c r="O11" s="37"/>
-      <c r="P11" s="37"/>
-      <c r="Q11" s="37"/>
-      <c r="R11" s="37"/>
+      <c r="J11" s="26"/>
+      <c r="K11" s="26"/>
+      <c r="M11" s="24"/>
+      <c r="N11" s="24"/>
+      <c r="O11" s="24"/>
+      <c r="P11" s="24"/>
+      <c r="Q11" s="24"/>
+      <c r="R11" s="24"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B12" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C12">
         <f t="shared" si="0"/>
@@ -2180,19 +2180,19 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G12))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>22</v>
       </c>
-      <c r="J12" s="39"/>
-      <c r="K12" s="39"/>
-      <c r="M12" s="37"/>
-      <c r="N12" s="37"/>
-      <c r="O12" s="37"/>
-      <c r="P12" s="37"/>
-      <c r="Q12" s="37"/>
-      <c r="R12" s="37"/>
+      <c r="J12" s="26"/>
+      <c r="K12" s="26"/>
+      <c r="M12" s="24"/>
+      <c r="N12" s="24"/>
+      <c r="O12" s="24"/>
+      <c r="P12" s="24"/>
+      <c r="Q12" s="24"/>
+      <c r="R12" s="24"/>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B13" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C13">
         <f t="shared" si="0"/>
@@ -2214,19 +2214,19 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G13))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>13.5</v>
       </c>
-      <c r="J13" s="39"/>
-      <c r="K13" s="39"/>
-      <c r="M13" s="37"/>
-      <c r="N13" s="37"/>
-      <c r="O13" s="37"/>
-      <c r="P13" s="37"/>
-      <c r="Q13" s="37"/>
-      <c r="R13" s="37"/>
+      <c r="J13" s="26"/>
+      <c r="K13" s="26"/>
+      <c r="M13" s="24"/>
+      <c r="N13" s="24"/>
+      <c r="O13" s="24"/>
+      <c r="P13" s="24"/>
+      <c r="Q13" s="24"/>
+      <c r="R13" s="24"/>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B14" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C14">
         <f t="shared" si="0"/>
@@ -2245,19 +2245,19 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G14))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>426</v>
       </c>
-      <c r="J14" s="39"/>
-      <c r="K14" s="39"/>
-      <c r="M14" s="37"/>
-      <c r="N14" s="37"/>
-      <c r="O14" s="37"/>
-      <c r="P14" s="37"/>
-      <c r="Q14" s="37"/>
-      <c r="R14" s="37"/>
+      <c r="J14" s="26"/>
+      <c r="K14" s="26"/>
+      <c r="M14" s="24"/>
+      <c r="N14" s="24"/>
+      <c r="O14" s="24"/>
+      <c r="P14" s="24"/>
+      <c r="Q14" s="24"/>
+      <c r="R14" s="24"/>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B15" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C15">
         <f t="shared" si="0"/>
@@ -2276,17 +2276,17 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G15))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>143</v>
       </c>
-      <c r="M15" s="37"/>
-      <c r="N15" s="37"/>
-      <c r="O15" s="37"/>
-      <c r="P15" s="37"/>
-      <c r="Q15" s="37"/>
-      <c r="R15" s="37"/>
+      <c r="M15" s="24"/>
+      <c r="N15" s="24"/>
+      <c r="O15" s="24"/>
+      <c r="P15" s="24"/>
+      <c r="Q15" s="24"/>
+      <c r="R15" s="24"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B16" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C16">
         <f t="shared" si="0"/>
@@ -2305,17 +2305,17 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G16))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>52</v>
       </c>
-      <c r="M16" s="37"/>
-      <c r="N16" s="37"/>
-      <c r="O16" s="37"/>
-      <c r="P16" s="37"/>
-      <c r="Q16" s="37"/>
-      <c r="R16" s="37"/>
+      <c r="M16" s="24"/>
+      <c r="N16" s="24"/>
+      <c r="O16" s="24"/>
+      <c r="P16" s="24"/>
+      <c r="Q16" s="24"/>
+      <c r="R16" s="24"/>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B17" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C17">
         <f t="shared" si="0"/>
@@ -2334,17 +2334,17 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G17))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>50</v>
       </c>
-      <c r="M17" s="37"/>
-      <c r="N17" s="37"/>
-      <c r="O17" s="37"/>
-      <c r="P17" s="37"/>
-      <c r="Q17" s="37"/>
-      <c r="R17" s="37"/>
+      <c r="M17" s="24"/>
+      <c r="N17" s="24"/>
+      <c r="O17" s="24"/>
+      <c r="P17" s="24"/>
+      <c r="Q17" s="24"/>
+      <c r="R17" s="24"/>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B18" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C18">
         <f t="shared" si="0"/>
@@ -2363,17 +2363,17 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G18))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>280</v>
       </c>
-      <c r="M18" s="37"/>
-      <c r="N18" s="37"/>
-      <c r="O18" s="37"/>
-      <c r="P18" s="37"/>
-      <c r="Q18" s="37"/>
-      <c r="R18" s="37"/>
+      <c r="M18" s="24"/>
+      <c r="N18" s="24"/>
+      <c r="O18" s="24"/>
+      <c r="P18" s="24"/>
+      <c r="Q18" s="24"/>
+      <c r="R18" s="24"/>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B19" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C19">
         <f t="shared" si="0"/>
@@ -2392,17 +2392,17 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G19))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>52</v>
       </c>
-      <c r="M19" s="37"/>
-      <c r="N19" s="37"/>
-      <c r="O19" s="37"/>
-      <c r="P19" s="37"/>
-      <c r="Q19" s="37"/>
-      <c r="R19" s="37"/>
+      <c r="M19" s="24"/>
+      <c r="N19" s="24"/>
+      <c r="O19" s="24"/>
+      <c r="P19" s="24"/>
+      <c r="Q19" s="24"/>
+      <c r="R19" s="24"/>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B20" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C20">
         <f t="shared" si="0"/>
@@ -2424,12 +2424,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G20))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>18</v>
       </c>
-      <c r="M20" s="37"/>
-      <c r="N20" s="37"/>
-      <c r="O20" s="37"/>
-      <c r="P20" s="37"/>
-      <c r="Q20" s="37"/>
-      <c r="R20" s="37"/>
+      <c r="M20" s="24"/>
+      <c r="N20" s="24"/>
+      <c r="O20" s="24"/>
+      <c r="P20" s="24"/>
+      <c r="Q20" s="24"/>
+      <c r="R20" s="24"/>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B21" s="18" t="str">
@@ -2444,12 +2444,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G21))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M21" s="37"/>
-      <c r="N21" s="37"/>
-      <c r="O21" s="37"/>
-      <c r="P21" s="37"/>
-      <c r="Q21" s="37"/>
-      <c r="R21" s="37"/>
+      <c r="M21" s="24"/>
+      <c r="N21" s="24"/>
+      <c r="O21" s="24"/>
+      <c r="P21" s="24"/>
+      <c r="Q21" s="24"/>
+      <c r="R21" s="24"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B22" s="18" t="str">
@@ -2464,12 +2464,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G22))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M22" s="37"/>
-      <c r="N22" s="37"/>
-      <c r="O22" s="37"/>
-      <c r="P22" s="37"/>
-      <c r="Q22" s="37"/>
-      <c r="R22" s="37"/>
+      <c r="M22" s="24"/>
+      <c r="N22" s="24"/>
+      <c r="O22" s="24"/>
+      <c r="P22" s="24"/>
+      <c r="Q22" s="24"/>
+      <c r="R22" s="24"/>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B23" s="18" t="str">
@@ -2498,14 +2498,14 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G24))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M24" s="33" t="s">
+      <c r="M24" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="N24" s="33"/>
-      <c r="O24" s="33"/>
-      <c r="P24" s="33"/>
-      <c r="Q24" s="33"/>
-      <c r="R24" s="33"/>
+      <c r="N24" s="20"/>
+      <c r="O24" s="20"/>
+      <c r="P24" s="20"/>
+      <c r="Q24" s="20"/>
+      <c r="R24" s="20"/>
     </row>
     <row r="25" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B25" s="18" t="str">
@@ -2520,12 +2520,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G25))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M25" s="34"/>
-      <c r="N25" s="34"/>
-      <c r="O25" s="34"/>
-      <c r="P25" s="34"/>
-      <c r="Q25" s="34"/>
-      <c r="R25" s="34"/>
+      <c r="M25" s="21"/>
+      <c r="N25" s="21"/>
+      <c r="O25" s="21"/>
+      <c r="P25" s="21"/>
+      <c r="Q25" s="21"/>
+      <c r="R25" s="21"/>
     </row>
     <row r="26" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="18" t="str">
@@ -2540,18 +2540,18 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G26))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M26" s="32" t="s">
+      <c r="M26" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="N26" s="32"/>
+      <c r="N26" s="39"/>
       <c r="O26" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="P26" s="32" t="s">
+      <c r="P26" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="Q26" s="32"/>
-      <c r="R26" s="32"/>
+      <c r="Q26" s="39"/>
+      <c r="R26" s="39"/>
     </row>
     <row r="27" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B27" s="18" t="str">
@@ -2566,16 +2566,16 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G27))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M27" s="20" t="s">
+      <c r="M27" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="N27" s="21"/>
-      <c r="O27" s="24">
+      <c r="N27" s="28"/>
+      <c r="O27" s="31">
         <v>80</v>
       </c>
-      <c r="P27" s="26"/>
-      <c r="Q27" s="27"/>
-      <c r="R27" s="28"/>
+      <c r="P27" s="33"/>
+      <c r="Q27" s="34"/>
+      <c r="R27" s="35"/>
     </row>
     <row r="28" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B28" s="18" t="str">
@@ -2590,12 +2590,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G28))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M28" s="22"/>
-      <c r="N28" s="23"/>
-      <c r="O28" s="25"/>
-      <c r="P28" s="29"/>
-      <c r="Q28" s="30"/>
-      <c r="R28" s="31"/>
+      <c r="M28" s="29"/>
+      <c r="N28" s="30"/>
+      <c r="O28" s="32"/>
+      <c r="P28" s="36"/>
+      <c r="Q28" s="37"/>
+      <c r="R28" s="38"/>
     </row>
     <row r="29" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B29" s="18" t="str">
@@ -2610,12 +2610,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G29))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M29" s="20"/>
-      <c r="N29" s="21"/>
-      <c r="O29" s="24"/>
-      <c r="P29" s="26"/>
-      <c r="Q29" s="27"/>
-      <c r="R29" s="28"/>
+      <c r="M29" s="27"/>
+      <c r="N29" s="28"/>
+      <c r="O29" s="31"/>
+      <c r="P29" s="33"/>
+      <c r="Q29" s="34"/>
+      <c r="R29" s="35"/>
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B30" s="18" t="str">
@@ -2630,12 +2630,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G30))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M30" s="22"/>
-      <c r="N30" s="23"/>
-      <c r="O30" s="25"/>
-      <c r="P30" s="29"/>
-      <c r="Q30" s="30"/>
-      <c r="R30" s="31"/>
+      <c r="M30" s="29"/>
+      <c r="N30" s="30"/>
+      <c r="O30" s="32"/>
+      <c r="P30" s="36"/>
+      <c r="Q30" s="37"/>
+      <c r="R30" s="38"/>
     </row>
     <row r="31" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B31" s="18" t="str">
@@ -2650,12 +2650,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G31))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M31" s="20"/>
-      <c r="N31" s="21"/>
-      <c r="O31" s="24"/>
-      <c r="P31" s="26"/>
-      <c r="Q31" s="27"/>
-      <c r="R31" s="28"/>
+      <c r="M31" s="27"/>
+      <c r="N31" s="28"/>
+      <c r="O31" s="31"/>
+      <c r="P31" s="33"/>
+      <c r="Q31" s="34"/>
+      <c r="R31" s="35"/>
     </row>
     <row r="32" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B32" s="18" t="str">
@@ -2670,12 +2670,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G32))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M32" s="22"/>
-      <c r="N32" s="23"/>
-      <c r="O32" s="25"/>
-      <c r="P32" s="29"/>
-      <c r="Q32" s="30"/>
-      <c r="R32" s="31"/>
+      <c r="M32" s="29"/>
+      <c r="N32" s="30"/>
+      <c r="O32" s="32"/>
+      <c r="P32" s="36"/>
+      <c r="Q32" s="37"/>
+      <c r="R32" s="38"/>
     </row>
     <row r="33" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B33" s="18" t="str">
@@ -2690,12 +2690,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G33))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M33" s="20"/>
-      <c r="N33" s="21"/>
-      <c r="O33" s="24"/>
-      <c r="P33" s="26"/>
-      <c r="Q33" s="27"/>
-      <c r="R33" s="28"/>
+      <c r="M33" s="27"/>
+      <c r="N33" s="28"/>
+      <c r="O33" s="31"/>
+      <c r="P33" s="33"/>
+      <c r="Q33" s="34"/>
+      <c r="R33" s="35"/>
     </row>
     <row r="34" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B34" s="18" t="str">
@@ -2710,12 +2710,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G34))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M34" s="22"/>
-      <c r="N34" s="23"/>
-      <c r="O34" s="25"/>
-      <c r="P34" s="29"/>
-      <c r="Q34" s="30"/>
-      <c r="R34" s="31"/>
+      <c r="M34" s="29"/>
+      <c r="N34" s="30"/>
+      <c r="O34" s="32"/>
+      <c r="P34" s="36"/>
+      <c r="Q34" s="37"/>
+      <c r="R34" s="38"/>
     </row>
     <row r="35" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B35" s="18" t="str">
@@ -2730,12 +2730,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G35))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M35" s="20"/>
-      <c r="N35" s="21"/>
-      <c r="O35" s="24"/>
-      <c r="P35" s="26"/>
-      <c r="Q35" s="27"/>
-      <c r="R35" s="28"/>
+      <c r="M35" s="27"/>
+      <c r="N35" s="28"/>
+      <c r="O35" s="31"/>
+      <c r="P35" s="33"/>
+      <c r="Q35" s="34"/>
+      <c r="R35" s="35"/>
     </row>
     <row r="36" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B36" s="18" t="str">
@@ -2750,12 +2750,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G36))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M36" s="22"/>
-      <c r="N36" s="23"/>
-      <c r="O36" s="25"/>
-      <c r="P36" s="29"/>
-      <c r="Q36" s="30"/>
-      <c r="R36" s="31"/>
+      <c r="M36" s="29"/>
+      <c r="N36" s="30"/>
+      <c r="O36" s="32"/>
+      <c r="P36" s="36"/>
+      <c r="Q36" s="37"/>
+      <c r="R36" s="38"/>
     </row>
     <row r="37" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B37" s="18" t="str">
@@ -2770,12 +2770,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G37))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M37" s="20"/>
-      <c r="N37" s="21"/>
-      <c r="O37" s="24"/>
-      <c r="P37" s="26"/>
-      <c r="Q37" s="27"/>
-      <c r="R37" s="28"/>
+      <c r="M37" s="27"/>
+      <c r="N37" s="28"/>
+      <c r="O37" s="31"/>
+      <c r="P37" s="33"/>
+      <c r="Q37" s="34"/>
+      <c r="R37" s="35"/>
     </row>
     <row r="38" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B38" s="18" t="str">
@@ -2790,12 +2790,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G38))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M38" s="22"/>
-      <c r="N38" s="23"/>
-      <c r="O38" s="25"/>
-      <c r="P38" s="29"/>
-      <c r="Q38" s="30"/>
-      <c r="R38" s="31"/>
+      <c r="M38" s="29"/>
+      <c r="N38" s="30"/>
+      <c r="O38" s="32"/>
+      <c r="P38" s="36"/>
+      <c r="Q38" s="37"/>
+      <c r="R38" s="38"/>
     </row>
     <row r="39" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B39" s="18" t="str">
@@ -2810,12 +2810,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G39))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M39" s="20"/>
-      <c r="N39" s="21"/>
-      <c r="O39" s="24"/>
-      <c r="P39" s="26"/>
-      <c r="Q39" s="27"/>
-      <c r="R39" s="28"/>
+      <c r="M39" s="27"/>
+      <c r="N39" s="28"/>
+      <c r="O39" s="31"/>
+      <c r="P39" s="33"/>
+      <c r="Q39" s="34"/>
+      <c r="R39" s="35"/>
     </row>
     <row r="40" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B40" s="18" t="str">
@@ -2830,12 +2830,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G40))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M40" s="22"/>
-      <c r="N40" s="23"/>
-      <c r="O40" s="25"/>
-      <c r="P40" s="29"/>
-      <c r="Q40" s="30"/>
-      <c r="R40" s="31"/>
+      <c r="M40" s="29"/>
+      <c r="N40" s="30"/>
+      <c r="O40" s="32"/>
+      <c r="P40" s="36"/>
+      <c r="Q40" s="37"/>
+      <c r="R40" s="38"/>
     </row>
     <row r="41" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B41" s="18" t="str">
@@ -2850,12 +2850,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G41))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M41" s="20"/>
-      <c r="N41" s="21"/>
-      <c r="O41" s="24"/>
-      <c r="P41" s="26"/>
-      <c r="Q41" s="27"/>
-      <c r="R41" s="28"/>
+      <c r="M41" s="27"/>
+      <c r="N41" s="28"/>
+      <c r="O41" s="31"/>
+      <c r="P41" s="33"/>
+      <c r="Q41" s="34"/>
+      <c r="R41" s="35"/>
     </row>
     <row r="42" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B42" s="18" t="str">
@@ -2870,12 +2870,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G42))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M42" s="22"/>
-      <c r="N42" s="23"/>
-      <c r="O42" s="25"/>
-      <c r="P42" s="29"/>
-      <c r="Q42" s="30"/>
-      <c r="R42" s="31"/>
+      <c r="M42" s="29"/>
+      <c r="N42" s="30"/>
+      <c r="O42" s="32"/>
+      <c r="P42" s="36"/>
+      <c r="Q42" s="37"/>
+      <c r="R42" s="38"/>
     </row>
     <row r="43" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B43" s="18" t="str">
@@ -2890,12 +2890,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G43))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M43" s="20"/>
-      <c r="N43" s="21"/>
-      <c r="O43" s="24"/>
-      <c r="P43" s="26"/>
-      <c r="Q43" s="27"/>
-      <c r="R43" s="28"/>
+      <c r="M43" s="27"/>
+      <c r="N43" s="28"/>
+      <c r="O43" s="31"/>
+      <c r="P43" s="33"/>
+      <c r="Q43" s="34"/>
+      <c r="R43" s="35"/>
     </row>
     <row r="44" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B44" s="18" t="str">
@@ -2910,12 +2910,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G44))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M44" s="22"/>
-      <c r="N44" s="23"/>
-      <c r="O44" s="25"/>
-      <c r="P44" s="29"/>
-      <c r="Q44" s="30"/>
-      <c r="R44" s="31"/>
+      <c r="M44" s="29"/>
+      <c r="N44" s="30"/>
+      <c r="O44" s="32"/>
+      <c r="P44" s="36"/>
+      <c r="Q44" s="37"/>
+      <c r="R44" s="38"/>
     </row>
     <row r="45" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B45" s="18" t="str">
@@ -2930,12 +2930,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G45))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M45" s="20"/>
-      <c r="N45" s="21"/>
-      <c r="O45" s="24"/>
-      <c r="P45" s="26"/>
-      <c r="Q45" s="27"/>
-      <c r="R45" s="28"/>
+      <c r="M45" s="27"/>
+      <c r="N45" s="28"/>
+      <c r="O45" s="31"/>
+      <c r="P45" s="33"/>
+      <c r="Q45" s="34"/>
+      <c r="R45" s="35"/>
     </row>
     <row r="46" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B46" s="18" t="str">
@@ -2950,12 +2950,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G46))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M46" s="22"/>
-      <c r="N46" s="23"/>
-      <c r="O46" s="25"/>
-      <c r="P46" s="29"/>
-      <c r="Q46" s="30"/>
-      <c r="R46" s="31"/>
+      <c r="M46" s="29"/>
+      <c r="N46" s="30"/>
+      <c r="O46" s="32"/>
+      <c r="P46" s="36"/>
+      <c r="Q46" s="37"/>
+      <c r="R46" s="38"/>
     </row>
     <row r="47" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B47" s="18" t="str">
@@ -2970,12 +2970,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G47))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M47" s="20"/>
-      <c r="N47" s="21"/>
-      <c r="O47" s="24"/>
-      <c r="P47" s="26"/>
-      <c r="Q47" s="27"/>
-      <c r="R47" s="28"/>
+      <c r="M47" s="27"/>
+      <c r="N47" s="28"/>
+      <c r="O47" s="31"/>
+      <c r="P47" s="33"/>
+      <c r="Q47" s="34"/>
+      <c r="R47" s="35"/>
     </row>
     <row r="48" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B48" s="18" t="str">
@@ -2990,12 +2990,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G48))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M48" s="22"/>
-      <c r="N48" s="23"/>
-      <c r="O48" s="25"/>
-      <c r="P48" s="29"/>
-      <c r="Q48" s="30"/>
-      <c r="R48" s="31"/>
+      <c r="M48" s="29"/>
+      <c r="N48" s="30"/>
+      <c r="O48" s="32"/>
+      <c r="P48" s="36"/>
+      <c r="Q48" s="37"/>
+      <c r="R48" s="38"/>
     </row>
     <row r="49" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B49" s="18" t="str">
@@ -3010,12 +3010,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G49))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M49" s="20"/>
-      <c r="N49" s="21"/>
-      <c r="O49" s="24"/>
-      <c r="P49" s="26"/>
-      <c r="Q49" s="27"/>
-      <c r="R49" s="28"/>
+      <c r="M49" s="27"/>
+      <c r="N49" s="28"/>
+      <c r="O49" s="31"/>
+      <c r="P49" s="33"/>
+      <c r="Q49" s="34"/>
+      <c r="R49" s="35"/>
     </row>
     <row r="50" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B50" s="18" t="str">
@@ -3030,12 +3030,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G50))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M50" s="22"/>
-      <c r="N50" s="23"/>
-      <c r="O50" s="25"/>
-      <c r="P50" s="29"/>
-      <c r="Q50" s="30"/>
-      <c r="R50" s="31"/>
+      <c r="M50" s="29"/>
+      <c r="N50" s="30"/>
+      <c r="O50" s="32"/>
+      <c r="P50" s="36"/>
+      <c r="Q50" s="37"/>
+      <c r="R50" s="38"/>
     </row>
     <row r="51" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B51" s="18" t="str">
@@ -3050,12 +3050,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G51))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M51" s="20"/>
-      <c r="N51" s="21"/>
-      <c r="O51" s="24"/>
-      <c r="P51" s="26"/>
-      <c r="Q51" s="27"/>
-      <c r="R51" s="28"/>
+      <c r="M51" s="27"/>
+      <c r="N51" s="28"/>
+      <c r="O51" s="31"/>
+      <c r="P51" s="33"/>
+      <c r="Q51" s="34"/>
+      <c r="R51" s="35"/>
     </row>
     <row r="52" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B52" s="18" t="str">
@@ -3070,12 +3070,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G52))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M52" s="22"/>
-      <c r="N52" s="23"/>
-      <c r="O52" s="25"/>
-      <c r="P52" s="29"/>
-      <c r="Q52" s="30"/>
-      <c r="R52" s="31"/>
+      <c r="M52" s="29"/>
+      <c r="N52" s="30"/>
+      <c r="O52" s="32"/>
+      <c r="P52" s="36"/>
+      <c r="Q52" s="37"/>
+      <c r="R52" s="38"/>
     </row>
     <row r="53" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B53" s="18" t="str">
@@ -3794,19 +3794,33 @@
   </sheetData>
   <autoFilter ref="B4" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="48">
-    <mergeCell ref="M24:R24"/>
-    <mergeCell ref="M25:R25"/>
-    <mergeCell ref="C2:H2"/>
-    <mergeCell ref="M4:R22"/>
-    <mergeCell ref="M2:R2"/>
-    <mergeCell ref="M3:R3"/>
-    <mergeCell ref="J5:K14"/>
-    <mergeCell ref="M41:N42"/>
-    <mergeCell ref="M43:N44"/>
-    <mergeCell ref="O41:O42"/>
-    <mergeCell ref="O43:O44"/>
-    <mergeCell ref="P41:R42"/>
-    <mergeCell ref="P43:R44"/>
+    <mergeCell ref="M49:N50"/>
+    <mergeCell ref="O49:O50"/>
+    <mergeCell ref="P49:R50"/>
+    <mergeCell ref="M51:N52"/>
+    <mergeCell ref="O51:O52"/>
+    <mergeCell ref="P51:R52"/>
+    <mergeCell ref="M45:N46"/>
+    <mergeCell ref="O45:O46"/>
+    <mergeCell ref="P45:R46"/>
+    <mergeCell ref="M47:N48"/>
+    <mergeCell ref="O47:O48"/>
+    <mergeCell ref="P47:R48"/>
+    <mergeCell ref="P31:R32"/>
+    <mergeCell ref="P33:R34"/>
+    <mergeCell ref="P35:R36"/>
+    <mergeCell ref="P37:R38"/>
+    <mergeCell ref="P39:R40"/>
+    <mergeCell ref="O31:O32"/>
+    <mergeCell ref="O33:O34"/>
+    <mergeCell ref="O35:O36"/>
+    <mergeCell ref="O37:O38"/>
+    <mergeCell ref="O39:O40"/>
+    <mergeCell ref="M31:N32"/>
+    <mergeCell ref="M33:N34"/>
+    <mergeCell ref="M35:N36"/>
+    <mergeCell ref="M37:N38"/>
+    <mergeCell ref="M39:N40"/>
     <mergeCell ref="P26:R26"/>
     <mergeCell ref="M26:N26"/>
     <mergeCell ref="M27:N28"/>
@@ -3815,33 +3829,19 @@
     <mergeCell ref="O29:O30"/>
     <mergeCell ref="P27:R28"/>
     <mergeCell ref="P29:R30"/>
-    <mergeCell ref="M31:N32"/>
-    <mergeCell ref="M33:N34"/>
-    <mergeCell ref="M35:N36"/>
-    <mergeCell ref="M37:N38"/>
-    <mergeCell ref="M39:N40"/>
-    <mergeCell ref="O31:O32"/>
-    <mergeCell ref="O33:O34"/>
-    <mergeCell ref="O35:O36"/>
-    <mergeCell ref="O37:O38"/>
-    <mergeCell ref="O39:O40"/>
-    <mergeCell ref="P31:R32"/>
-    <mergeCell ref="P33:R34"/>
-    <mergeCell ref="P35:R36"/>
-    <mergeCell ref="P37:R38"/>
-    <mergeCell ref="P39:R40"/>
-    <mergeCell ref="M45:N46"/>
-    <mergeCell ref="O45:O46"/>
-    <mergeCell ref="P45:R46"/>
-    <mergeCell ref="M47:N48"/>
-    <mergeCell ref="O47:O48"/>
-    <mergeCell ref="P47:R48"/>
-    <mergeCell ref="M49:N50"/>
-    <mergeCell ref="O49:O50"/>
-    <mergeCell ref="P49:R50"/>
-    <mergeCell ref="M51:N52"/>
-    <mergeCell ref="O51:O52"/>
-    <mergeCell ref="P51:R52"/>
+    <mergeCell ref="M41:N42"/>
+    <mergeCell ref="M43:N44"/>
+    <mergeCell ref="O41:O42"/>
+    <mergeCell ref="O43:O44"/>
+    <mergeCell ref="P41:R42"/>
+    <mergeCell ref="P43:R44"/>
+    <mergeCell ref="M24:R24"/>
+    <mergeCell ref="M25:R25"/>
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="M4:R22"/>
+    <mergeCell ref="M2:R2"/>
+    <mergeCell ref="M3:R3"/>
+    <mergeCell ref="J5:K14"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B103">
     <cfRule type="expression" dxfId="13" priority="1">
@@ -3881,23 +3881,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="C2" s="35" t="s">
+      <c r="C2" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="D2" s="35"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
       <c r="L2" s="8"/>
-      <c r="M2" s="35" t="s">
+      <c r="M2" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="36"/>
-      <c r="O2" s="36"/>
-      <c r="P2" s="36"/>
-      <c r="Q2" s="36"/>
-      <c r="R2" s="36"/>
+      <c r="N2" s="23"/>
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
+      <c r="R2" s="23"/>
     </row>
     <row r="3" spans="2:18" ht="26.25" x14ac:dyDescent="0.4">
       <c r="G3" t="s">
@@ -3910,14 +3910,14 @@
         <f>SUM(Tabla110[Importa])</f>
         <v>2344</v>
       </c>
-      <c r="M3" s="38" t="s">
+      <c r="M3" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="38"/>
-      <c r="O3" s="38"/>
-      <c r="P3" s="38"/>
-      <c r="Q3" s="38"/>
-      <c r="R3" s="38"/>
+      <c r="N3" s="25"/>
+      <c r="O3" s="25"/>
+      <c r="P3" s="25"/>
+      <c r="Q3" s="25"/>
+      <c r="R3" s="25"/>
     </row>
     <row r="4" spans="2:18" ht="33.75" x14ac:dyDescent="0.5">
       <c r="B4" s="17" t="s">
@@ -3948,19 +3948,19 @@
         <f>COUNTIF(C5:C103,"&gt;0")</f>
         <v>21</v>
       </c>
-      <c r="M4" s="37" t="s">
+      <c r="M4" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="N4" s="37"/>
-      <c r="O4" s="37"/>
-      <c r="P4" s="37"/>
-      <c r="Q4" s="37"/>
-      <c r="R4" s="37"/>
+      <c r="N4" s="24"/>
+      <c r="O4" s="24"/>
+      <c r="P4" s="24"/>
+      <c r="Q4" s="24"/>
+      <c r="R4" s="24"/>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B5" s="18">
         <f ca="1">IF(Tabla110[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C5">
         <f t="shared" ref="C5:C68" si="0">IF(ISNUMBER(E5), IF(ISNUMBER(C4), C4+1, 1), "")</f>
@@ -3982,21 +3982,21 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G5))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>67.5</v>
       </c>
-      <c r="J5" s="39" t="s">
+      <c r="J5" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="K5" s="39"/>
-      <c r="M5" s="37"/>
-      <c r="N5" s="37"/>
-      <c r="O5" s="37"/>
-      <c r="P5" s="37"/>
-      <c r="Q5" s="37"/>
-      <c r="R5" s="37"/>
+      <c r="K5" s="26"/>
+      <c r="M5" s="24"/>
+      <c r="N5" s="24"/>
+      <c r="O5" s="24"/>
+      <c r="P5" s="24"/>
+      <c r="Q5" s="24"/>
+      <c r="R5" s="24"/>
     </row>
     <row r="6" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C6">
         <f t="shared" si="0"/>
@@ -4018,19 +4018,19 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G6))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>90</v>
       </c>
-      <c r="J6" s="39"/>
-      <c r="K6" s="39"/>
-      <c r="M6" s="37"/>
-      <c r="N6" s="37"/>
-      <c r="O6" s="37"/>
-      <c r="P6" s="37"/>
-      <c r="Q6" s="37"/>
-      <c r="R6" s="37"/>
+      <c r="J6" s="26"/>
+      <c r="K6" s="26"/>
+      <c r="M6" s="24"/>
+      <c r="N6" s="24"/>
+      <c r="O6" s="24"/>
+      <c r="P6" s="24"/>
+      <c r="Q6" s="24"/>
+      <c r="R6" s="24"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B7" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
@@ -4052,19 +4052,19 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G7))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>126</v>
       </c>
-      <c r="J7" s="39"/>
-      <c r="K7" s="39"/>
-      <c r="M7" s="37"/>
-      <c r="N7" s="37"/>
-      <c r="O7" s="37"/>
-      <c r="P7" s="37"/>
-      <c r="Q7" s="37"/>
-      <c r="R7" s="37"/>
+      <c r="J7" s="26"/>
+      <c r="K7" s="26"/>
+      <c r="M7" s="24"/>
+      <c r="N7" s="24"/>
+      <c r="O7" s="24"/>
+      <c r="P7" s="24"/>
+      <c r="Q7" s="24"/>
+      <c r="R7" s="24"/>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B8" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C8">
         <f t="shared" si="0"/>
@@ -4086,19 +4086,19 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G8))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>54</v>
       </c>
-      <c r="J8" s="39"/>
-      <c r="K8" s="39"/>
-      <c r="M8" s="37"/>
-      <c r="N8" s="37"/>
-      <c r="O8" s="37"/>
-      <c r="P8" s="37"/>
-      <c r="Q8" s="37"/>
-      <c r="R8" s="37"/>
+      <c r="J8" s="26"/>
+      <c r="K8" s="26"/>
+      <c r="M8" s="24"/>
+      <c r="N8" s="24"/>
+      <c r="O8" s="24"/>
+      <c r="P8" s="24"/>
+      <c r="Q8" s="24"/>
+      <c r="R8" s="24"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B9" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C9">
         <f t="shared" si="0"/>
@@ -4120,19 +4120,19 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G9))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>49.5</v>
       </c>
-      <c r="J9" s="39"/>
-      <c r="K9" s="39"/>
-      <c r="M9" s="37"/>
-      <c r="N9" s="37"/>
-      <c r="O9" s="37"/>
-      <c r="P9" s="37"/>
-      <c r="Q9" s="37"/>
-      <c r="R9" s="37"/>
+      <c r="J9" s="26"/>
+      <c r="K9" s="26"/>
+      <c r="M9" s="24"/>
+      <c r="N9" s="24"/>
+      <c r="O9" s="24"/>
+      <c r="P9" s="24"/>
+      <c r="Q9" s="24"/>
+      <c r="R9" s="24"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B10" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C10">
         <f t="shared" si="0"/>
@@ -4151,19 +4151,19 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G10))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>10</v>
       </c>
-      <c r="J10" s="39"/>
-      <c r="K10" s="39"/>
-      <c r="M10" s="37"/>
-      <c r="N10" s="37"/>
-      <c r="O10" s="37"/>
-      <c r="P10" s="37"/>
-      <c r="Q10" s="37"/>
-      <c r="R10" s="37"/>
+      <c r="J10" s="26"/>
+      <c r="K10" s="26"/>
+      <c r="M10" s="24"/>
+      <c r="N10" s="24"/>
+      <c r="O10" s="24"/>
+      <c r="P10" s="24"/>
+      <c r="Q10" s="24"/>
+      <c r="R10" s="24"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B11" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C11">
         <f t="shared" si="0"/>
@@ -4182,19 +4182,19 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G11))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>5</v>
       </c>
-      <c r="J11" s="39"/>
-      <c r="K11" s="39"/>
-      <c r="M11" s="37"/>
-      <c r="N11" s="37"/>
-      <c r="O11" s="37"/>
-      <c r="P11" s="37"/>
-      <c r="Q11" s="37"/>
-      <c r="R11" s="37"/>
+      <c r="J11" s="26"/>
+      <c r="K11" s="26"/>
+      <c r="M11" s="24"/>
+      <c r="N11" s="24"/>
+      <c r="O11" s="24"/>
+      <c r="P11" s="24"/>
+      <c r="Q11" s="24"/>
+      <c r="R11" s="24"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B12" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C12">
         <f t="shared" si="0"/>
@@ -4213,19 +4213,19 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G12))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>3</v>
       </c>
-      <c r="J12" s="39"/>
-      <c r="K12" s="39"/>
-      <c r="M12" s="37"/>
-      <c r="N12" s="37"/>
-      <c r="O12" s="37"/>
-      <c r="P12" s="37"/>
-      <c r="Q12" s="37"/>
-      <c r="R12" s="37"/>
+      <c r="J12" s="26"/>
+      <c r="K12" s="26"/>
+      <c r="M12" s="24"/>
+      <c r="N12" s="24"/>
+      <c r="O12" s="24"/>
+      <c r="P12" s="24"/>
+      <c r="Q12" s="24"/>
+      <c r="R12" s="24"/>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B13" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C13">
         <f t="shared" si="0"/>
@@ -4244,19 +4244,19 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G13))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>35</v>
       </c>
-      <c r="J13" s="39"/>
-      <c r="K13" s="39"/>
-      <c r="M13" s="37"/>
-      <c r="N13" s="37"/>
-      <c r="O13" s="37"/>
-      <c r="P13" s="37"/>
-      <c r="Q13" s="37"/>
-      <c r="R13" s="37"/>
+      <c r="J13" s="26"/>
+      <c r="K13" s="26"/>
+      <c r="M13" s="24"/>
+      <c r="N13" s="24"/>
+      <c r="O13" s="24"/>
+      <c r="P13" s="24"/>
+      <c r="Q13" s="24"/>
+      <c r="R13" s="24"/>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B14" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C14">
         <f t="shared" si="0"/>
@@ -4275,19 +4275,19 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G14))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>10</v>
       </c>
-      <c r="J14" s="39"/>
-      <c r="K14" s="39"/>
-      <c r="M14" s="37"/>
-      <c r="N14" s="37"/>
-      <c r="O14" s="37"/>
-      <c r="P14" s="37"/>
-      <c r="Q14" s="37"/>
-      <c r="R14" s="37"/>
+      <c r="J14" s="26"/>
+      <c r="K14" s="26"/>
+      <c r="M14" s="24"/>
+      <c r="N14" s="24"/>
+      <c r="O14" s="24"/>
+      <c r="P14" s="24"/>
+      <c r="Q14" s="24"/>
+      <c r="R14" s="24"/>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B15" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C15">
         <f t="shared" si="0"/>
@@ -4306,17 +4306,17 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G15))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>135</v>
       </c>
-      <c r="M15" s="37"/>
-      <c r="N15" s="37"/>
-      <c r="O15" s="37"/>
-      <c r="P15" s="37"/>
-      <c r="Q15" s="37"/>
-      <c r="R15" s="37"/>
+      <c r="M15" s="24"/>
+      <c r="N15" s="24"/>
+      <c r="O15" s="24"/>
+      <c r="P15" s="24"/>
+      <c r="Q15" s="24"/>
+      <c r="R15" s="24"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B16" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C16">
         <f t="shared" si="0"/>
@@ -4335,17 +4335,17 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G16))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>650</v>
       </c>
-      <c r="M16" s="37"/>
-      <c r="N16" s="37"/>
-      <c r="O16" s="37"/>
-      <c r="P16" s="37"/>
-      <c r="Q16" s="37"/>
-      <c r="R16" s="37"/>
+      <c r="M16" s="24"/>
+      <c r="N16" s="24"/>
+      <c r="O16" s="24"/>
+      <c r="P16" s="24"/>
+      <c r="Q16" s="24"/>
+      <c r="R16" s="24"/>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B17" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C17">
         <f t="shared" si="0"/>
@@ -4364,17 +4364,17 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G17))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>261</v>
       </c>
-      <c r="M17" s="37"/>
-      <c r="N17" s="37"/>
-      <c r="O17" s="37"/>
-      <c r="P17" s="37"/>
-      <c r="Q17" s="37"/>
-      <c r="R17" s="37"/>
+      <c r="M17" s="24"/>
+      <c r="N17" s="24"/>
+      <c r="O17" s="24"/>
+      <c r="P17" s="24"/>
+      <c r="Q17" s="24"/>
+      <c r="R17" s="24"/>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B18" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C18">
         <f t="shared" si="0"/>
@@ -4396,17 +4396,17 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G18))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>111.5</v>
       </c>
-      <c r="M18" s="37"/>
-      <c r="N18" s="37"/>
-      <c r="O18" s="37"/>
-      <c r="P18" s="37"/>
-      <c r="Q18" s="37"/>
-      <c r="R18" s="37"/>
+      <c r="M18" s="24"/>
+      <c r="N18" s="24"/>
+      <c r="O18" s="24"/>
+      <c r="P18" s="24"/>
+      <c r="Q18" s="24"/>
+      <c r="R18" s="24"/>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B19" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C19">
         <f t="shared" si="0"/>
@@ -4428,17 +4428,17 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G19))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>27</v>
       </c>
-      <c r="M19" s="37"/>
-      <c r="N19" s="37"/>
-      <c r="O19" s="37"/>
-      <c r="P19" s="37"/>
-      <c r="Q19" s="37"/>
-      <c r="R19" s="37"/>
+      <c r="M19" s="24"/>
+      <c r="N19" s="24"/>
+      <c r="O19" s="24"/>
+      <c r="P19" s="24"/>
+      <c r="Q19" s="24"/>
+      <c r="R19" s="24"/>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B20" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C20">
         <f t="shared" si="0"/>
@@ -4460,12 +4460,12 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G20))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>97.5</v>
       </c>
-      <c r="M20" s="37"/>
-      <c r="N20" s="37"/>
-      <c r="O20" s="37"/>
-      <c r="P20" s="37"/>
-      <c r="Q20" s="37"/>
-      <c r="R20" s="37"/>
+      <c r="M20" s="24"/>
+      <c r="N20" s="24"/>
+      <c r="O20" s="24"/>
+      <c r="P20" s="24"/>
+      <c r="Q20" s="24"/>
+      <c r="R20" s="24"/>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B21" s="18" t="str">
@@ -4489,12 +4489,12 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G21))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>142</v>
       </c>
-      <c r="M21" s="37"/>
-      <c r="N21" s="37"/>
-      <c r="O21" s="37"/>
-      <c r="P21" s="37"/>
-      <c r="Q21" s="37"/>
-      <c r="R21" s="37"/>
+      <c r="M21" s="24"/>
+      <c r="N21" s="24"/>
+      <c r="O21" s="24"/>
+      <c r="P21" s="24"/>
+      <c r="Q21" s="24"/>
+      <c r="R21" s="24"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B22" s="18" t="str">
@@ -4521,12 +4521,12 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G22))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>27</v>
       </c>
-      <c r="M22" s="37"/>
-      <c r="N22" s="37"/>
-      <c r="O22" s="37"/>
-      <c r="P22" s="37"/>
-      <c r="Q22" s="37"/>
-      <c r="R22" s="37"/>
+      <c r="M22" s="24"/>
+      <c r="N22" s="24"/>
+      <c r="O22" s="24"/>
+      <c r="P22" s="24"/>
+      <c r="Q22" s="24"/>
+      <c r="R22" s="24"/>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B23" s="18" t="str">
@@ -4576,14 +4576,14 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G24))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>150</v>
       </c>
-      <c r="M24" s="33" t="s">
+      <c r="M24" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="N24" s="46"/>
-      <c r="O24" s="46"/>
-      <c r="P24" s="46"/>
-      <c r="Q24" s="46"/>
-      <c r="R24" s="46"/>
+      <c r="N24" s="40"/>
+      <c r="O24" s="40"/>
+      <c r="P24" s="40"/>
+      <c r="Q24" s="40"/>
+      <c r="R24" s="40"/>
     </row>
     <row r="25" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B25" s="18" t="str">
@@ -4607,12 +4607,12 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G25))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>50</v>
       </c>
-      <c r="M25" s="38"/>
-      <c r="N25" s="38"/>
-      <c r="O25" s="38"/>
-      <c r="P25" s="38"/>
-      <c r="Q25" s="38"/>
-      <c r="R25" s="38"/>
+      <c r="M25" s="25"/>
+      <c r="N25" s="25"/>
+      <c r="O25" s="25"/>
+      <c r="P25" s="25"/>
+      <c r="Q25" s="25"/>
+      <c r="R25" s="25"/>
     </row>
     <row r="26" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B26" s="18" t="str">
@@ -4629,12 +4629,12 @@
       <c r="N26" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="O26" s="32" t="s">
+      <c r="O26" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="P26" s="32"/>
-      <c r="Q26" s="32"/>
-      <c r="R26" s="32"/>
+      <c r="P26" s="39"/>
+      <c r="Q26" s="39"/>
+      <c r="R26" s="39"/>
     </row>
     <row r="27" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B27" s="18" t="str">
@@ -4651,10 +4651,10 @@
       <c r="N27" s="15">
         <v>160</v>
       </c>
-      <c r="O27" s="40"/>
-      <c r="P27" s="41"/>
-      <c r="Q27" s="41"/>
-      <c r="R27" s="42"/>
+      <c r="O27" s="41"/>
+      <c r="P27" s="42"/>
+      <c r="Q27" s="42"/>
+      <c r="R27" s="43"/>
     </row>
     <row r="28" spans="2:18" ht="30" x14ac:dyDescent="0.25">
       <c r="B28" s="18" t="str">
@@ -4671,10 +4671,10 @@
       <c r="N28" s="15">
         <v>2030</v>
       </c>
-      <c r="O28" s="40"/>
-      <c r="P28" s="41"/>
-      <c r="Q28" s="41"/>
-      <c r="R28" s="42"/>
+      <c r="O28" s="41"/>
+      <c r="P28" s="42"/>
+      <c r="Q28" s="42"/>
+      <c r="R28" s="43"/>
     </row>
     <row r="29" spans="2:18" ht="30" x14ac:dyDescent="0.25">
       <c r="B29" s="18" t="str">
@@ -4695,10 +4695,10 @@
       <c r="N29" s="15">
         <v>1492</v>
       </c>
-      <c r="O29" s="40"/>
-      <c r="P29" s="41"/>
-      <c r="Q29" s="41"/>
-      <c r="R29" s="42"/>
+      <c r="O29" s="41"/>
+      <c r="P29" s="42"/>
+      <c r="Q29" s="42"/>
+      <c r="R29" s="43"/>
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B30" s="18" t="str">
@@ -4723,10 +4723,10 @@
       <c r="N30" s="15">
         <v>1550</v>
       </c>
-      <c r="O30" s="40"/>
-      <c r="P30" s="41"/>
-      <c r="Q30" s="41"/>
-      <c r="R30" s="42"/>
+      <c r="O30" s="41"/>
+      <c r="P30" s="42"/>
+      <c r="Q30" s="42"/>
+      <c r="R30" s="43"/>
     </row>
     <row r="31" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B31" s="18" t="str">
@@ -4751,12 +4751,12 @@
       <c r="N31" s="19">
         <v>5232</v>
       </c>
-      <c r="O31" s="43" t="s">
+      <c r="O31" s="44" t="s">
         <v>64</v>
       </c>
-      <c r="P31" s="44"/>
-      <c r="Q31" s="44"/>
-      <c r="R31" s="45"/>
+      <c r="P31" s="45"/>
+      <c r="Q31" s="45"/>
+      <c r="R31" s="46"/>
     </row>
     <row r="32" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B32" s="18" t="str">
@@ -4777,10 +4777,10 @@
       </c>
       <c r="M32" s="13"/>
       <c r="N32" s="15"/>
-      <c r="O32" s="40"/>
-      <c r="P32" s="41"/>
-      <c r="Q32" s="41"/>
-      <c r="R32" s="42"/>
+      <c r="O32" s="41"/>
+      <c r="P32" s="42"/>
+      <c r="Q32" s="42"/>
+      <c r="R32" s="43"/>
     </row>
     <row r="33" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B33" s="18" t="str">
@@ -4801,10 +4801,10 @@
       </c>
       <c r="M33" s="13"/>
       <c r="N33" s="15"/>
-      <c r="O33" s="40"/>
-      <c r="P33" s="41"/>
-      <c r="Q33" s="41"/>
-      <c r="R33" s="42"/>
+      <c r="O33" s="41"/>
+      <c r="P33" s="42"/>
+      <c r="Q33" s="42"/>
+      <c r="R33" s="43"/>
     </row>
     <row r="34" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B34" s="18" t="str">
@@ -4825,10 +4825,10 @@
       </c>
       <c r="M34" s="13"/>
       <c r="N34" s="15"/>
-      <c r="O34" s="40"/>
-      <c r="P34" s="41"/>
-      <c r="Q34" s="41"/>
-      <c r="R34" s="42"/>
+      <c r="O34" s="41"/>
+      <c r="P34" s="42"/>
+      <c r="Q34" s="42"/>
+      <c r="R34" s="43"/>
     </row>
     <row r="35" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B35" s="18" t="str">
@@ -4845,10 +4845,10 @@
       </c>
       <c r="M35" s="13"/>
       <c r="N35" s="15"/>
-      <c r="O35" s="40"/>
-      <c r="P35" s="41"/>
-      <c r="Q35" s="41"/>
-      <c r="R35" s="42"/>
+      <c r="O35" s="41"/>
+      <c r="P35" s="42"/>
+      <c r="Q35" s="42"/>
+      <c r="R35" s="43"/>
     </row>
     <row r="36" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B36" s="18" t="str">
@@ -4865,10 +4865,10 @@
       </c>
       <c r="M36" s="13"/>
       <c r="N36" s="15"/>
-      <c r="O36" s="40"/>
-      <c r="P36" s="41"/>
-      <c r="Q36" s="41"/>
-      <c r="R36" s="42"/>
+      <c r="O36" s="41"/>
+      <c r="P36" s="42"/>
+      <c r="Q36" s="42"/>
+      <c r="R36" s="43"/>
     </row>
     <row r="37" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B37" s="18" t="str">
@@ -4885,10 +4885,10 @@
       </c>
       <c r="M37" s="13"/>
       <c r="N37" s="15"/>
-      <c r="O37" s="40"/>
-      <c r="P37" s="41"/>
-      <c r="Q37" s="41"/>
-      <c r="R37" s="42"/>
+      <c r="O37" s="41"/>
+      <c r="P37" s="42"/>
+      <c r="Q37" s="42"/>
+      <c r="R37" s="43"/>
     </row>
     <row r="38" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B38" s="18" t="str">
@@ -4905,10 +4905,10 @@
       </c>
       <c r="M38" s="13"/>
       <c r="N38" s="15"/>
-      <c r="O38" s="40"/>
-      <c r="P38" s="41"/>
-      <c r="Q38" s="41"/>
-      <c r="R38" s="42"/>
+      <c r="O38" s="41"/>
+      <c r="P38" s="42"/>
+      <c r="Q38" s="42"/>
+      <c r="R38" s="43"/>
     </row>
     <row r="39" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B39" s="18" t="str">
@@ -4925,10 +4925,10 @@
       </c>
       <c r="M39" s="13"/>
       <c r="N39" s="15"/>
-      <c r="O39" s="40"/>
-      <c r="P39" s="41"/>
-      <c r="Q39" s="41"/>
-      <c r="R39" s="42"/>
+      <c r="O39" s="41"/>
+      <c r="P39" s="42"/>
+      <c r="Q39" s="42"/>
+      <c r="R39" s="43"/>
     </row>
     <row r="40" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B40" s="18" t="str">
@@ -4945,10 +4945,10 @@
       </c>
       <c r="M40" s="13"/>
       <c r="N40" s="15"/>
-      <c r="O40" s="40"/>
-      <c r="P40" s="41"/>
-      <c r="Q40" s="41"/>
-      <c r="R40" s="42"/>
+      <c r="O40" s="41"/>
+      <c r="P40" s="42"/>
+      <c r="Q40" s="42"/>
+      <c r="R40" s="43"/>
     </row>
     <row r="41" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B41" s="18" t="str">
@@ -4965,10 +4965,10 @@
       </c>
       <c r="M41" s="13"/>
       <c r="N41" s="15"/>
-      <c r="O41" s="40"/>
-      <c r="P41" s="41"/>
-      <c r="Q41" s="41"/>
-      <c r="R41" s="42"/>
+      <c r="O41" s="41"/>
+      <c r="P41" s="42"/>
+      <c r="Q41" s="42"/>
+      <c r="R41" s="43"/>
     </row>
     <row r="42" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B42" s="18" t="str">
@@ -4985,10 +4985,10 @@
       </c>
       <c r="M42" s="13"/>
       <c r="N42" s="15"/>
-      <c r="O42" s="40"/>
-      <c r="P42" s="41"/>
-      <c r="Q42" s="41"/>
-      <c r="R42" s="42"/>
+      <c r="O42" s="41"/>
+      <c r="P42" s="42"/>
+      <c r="Q42" s="42"/>
+      <c r="R42" s="43"/>
     </row>
     <row r="43" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B43" s="18" t="str">
@@ -5005,10 +5005,10 @@
       </c>
       <c r="M43" s="13"/>
       <c r="N43" s="15"/>
-      <c r="O43" s="40"/>
-      <c r="P43" s="41"/>
-      <c r="Q43" s="41"/>
-      <c r="R43" s="42"/>
+      <c r="O43" s="41"/>
+      <c r="P43" s="42"/>
+      <c r="Q43" s="42"/>
+      <c r="R43" s="43"/>
     </row>
     <row r="44" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B44" s="18" t="str">
@@ -5025,10 +5025,10 @@
       </c>
       <c r="M44" s="13"/>
       <c r="N44" s="15"/>
-      <c r="O44" s="40"/>
-      <c r="P44" s="41"/>
-      <c r="Q44" s="41"/>
-      <c r="R44" s="42"/>
+      <c r="O44" s="41"/>
+      <c r="P44" s="42"/>
+      <c r="Q44" s="42"/>
+      <c r="R44" s="43"/>
     </row>
     <row r="45" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B45" s="18" t="str">
@@ -5858,32 +5858,32 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="C2:H2"/>
-    <mergeCell ref="M2:R2"/>
-    <mergeCell ref="M3:R3"/>
-    <mergeCell ref="M4:R22"/>
-    <mergeCell ref="J5:K14"/>
-    <mergeCell ref="M24:R24"/>
-    <mergeCell ref="M25:R25"/>
-    <mergeCell ref="O26:R26"/>
-    <mergeCell ref="O27:R27"/>
-    <mergeCell ref="O28:R28"/>
-    <mergeCell ref="O29:R29"/>
-    <mergeCell ref="O30:R30"/>
-    <mergeCell ref="O31:R31"/>
-    <mergeCell ref="O32:R32"/>
-    <mergeCell ref="O33:R33"/>
-    <mergeCell ref="O34:R34"/>
-    <mergeCell ref="O35:R35"/>
-    <mergeCell ref="O36:R36"/>
-    <mergeCell ref="O37:R37"/>
-    <mergeCell ref="O38:R38"/>
     <mergeCell ref="O44:R44"/>
     <mergeCell ref="O39:R39"/>
     <mergeCell ref="O40:R40"/>
     <mergeCell ref="O41:R41"/>
     <mergeCell ref="O42:R42"/>
     <mergeCell ref="O43:R43"/>
+    <mergeCell ref="O34:R34"/>
+    <mergeCell ref="O35:R35"/>
+    <mergeCell ref="O36:R36"/>
+    <mergeCell ref="O37:R37"/>
+    <mergeCell ref="O38:R38"/>
+    <mergeCell ref="O29:R29"/>
+    <mergeCell ref="O30:R30"/>
+    <mergeCell ref="O31:R31"/>
+    <mergeCell ref="O32:R32"/>
+    <mergeCell ref="O33:R33"/>
+    <mergeCell ref="M24:R24"/>
+    <mergeCell ref="M25:R25"/>
+    <mergeCell ref="O26:R26"/>
+    <mergeCell ref="O27:R27"/>
+    <mergeCell ref="O28:R28"/>
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="M2:R2"/>
+    <mergeCell ref="M3:R3"/>
+    <mergeCell ref="M4:R22"/>
+    <mergeCell ref="J5:K14"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B103">
     <cfRule type="expression" dxfId="11" priority="1">
@@ -5922,23 +5922,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="C2" s="35" t="s">
+      <c r="C2" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="D2" s="35"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
       <c r="L2" s="8"/>
-      <c r="M2" s="35" t="s">
+      <c r="M2" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="36"/>
-      <c r="O2" s="36"/>
-      <c r="P2" s="36"/>
-      <c r="Q2" s="36"/>
-      <c r="R2" s="36"/>
+      <c r="N2" s="23"/>
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
+      <c r="R2" s="23"/>
     </row>
     <row r="3" spans="2:18" ht="26.25" x14ac:dyDescent="0.4">
       <c r="G3" t="s">
@@ -5951,14 +5951,14 @@
         <f>SUM(Tabla111[Importa])</f>
         <v>1547.5</v>
       </c>
-      <c r="M3" s="38" t="s">
+      <c r="M3" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="38"/>
-      <c r="O3" s="38"/>
-      <c r="P3" s="38"/>
-      <c r="Q3" s="38"/>
-      <c r="R3" s="38"/>
+      <c r="N3" s="25"/>
+      <c r="O3" s="25"/>
+      <c r="P3" s="25"/>
+      <c r="Q3" s="25"/>
+      <c r="R3" s="25"/>
     </row>
     <row r="4" spans="2:18" ht="33.75" x14ac:dyDescent="0.5">
       <c r="B4" s="17" t="s">
@@ -5989,19 +5989,19 @@
         <f>COUNTIF(C5:C103,"&gt;0")</f>
         <v>19</v>
       </c>
-      <c r="M4" s="37" t="s">
+      <c r="M4" s="24" t="s">
         <v>82</v>
       </c>
-      <c r="N4" s="37"/>
-      <c r="O4" s="37"/>
-      <c r="P4" s="37"/>
-      <c r="Q4" s="37"/>
-      <c r="R4" s="37"/>
+      <c r="N4" s="24"/>
+      <c r="O4" s="24"/>
+      <c r="P4" s="24"/>
+      <c r="Q4" s="24"/>
+      <c r="R4" s="24"/>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B5" s="18">
         <f ca="1">IF(Tabla111[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C5">
         <f>IF(ISNUMBER(E5), IF(ISNUMBER(C4), C4+1, 1), "")</f>
@@ -6020,21 +6020,21 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G5))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>20</v>
       </c>
-      <c r="J5" s="39" t="s">
+      <c r="J5" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="K5" s="39"/>
-      <c r="M5" s="37"/>
-      <c r="N5" s="37"/>
-      <c r="O5" s="37"/>
-      <c r="P5" s="37"/>
-      <c r="Q5" s="37"/>
-      <c r="R5" s="37"/>
+      <c r="K5" s="26"/>
+      <c r="M5" s="24"/>
+      <c r="N5" s="24"/>
+      <c r="O5" s="24"/>
+      <c r="P5" s="24"/>
+      <c r="Q5" s="24"/>
+      <c r="R5" s="24"/>
     </row>
     <row r="6" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C6">
         <f t="shared" ref="C6" si="0">IF(ISNUMBER(E6), IF(ISNUMBER(C5), C5+1, 1), "")</f>
@@ -6053,19 +6053,19 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G6))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>42</v>
       </c>
-      <c r="J6" s="39"/>
-      <c r="K6" s="39"/>
-      <c r="M6" s="37"/>
-      <c r="N6" s="37"/>
-      <c r="O6" s="37"/>
-      <c r="P6" s="37"/>
-      <c r="Q6" s="37"/>
-      <c r="R6" s="37"/>
+      <c r="J6" s="26"/>
+      <c r="K6" s="26"/>
+      <c r="M6" s="24"/>
+      <c r="N6" s="24"/>
+      <c r="O6" s="24"/>
+      <c r="P6" s="24"/>
+      <c r="Q6" s="24"/>
+      <c r="R6" s="24"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B7" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C7">
         <f>IF(ISNUMBER(E7), IF(ISNUMBER(C6), C6+1, 1), "")</f>
@@ -6084,19 +6084,19 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G7))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>95</v>
       </c>
-      <c r="J7" s="39"/>
-      <c r="K7" s="39"/>
-      <c r="M7" s="37"/>
-      <c r="N7" s="37"/>
-      <c r="O7" s="37"/>
-      <c r="P7" s="37"/>
-      <c r="Q7" s="37"/>
-      <c r="R7" s="37"/>
+      <c r="J7" s="26"/>
+      <c r="K7" s="26"/>
+      <c r="M7" s="24"/>
+      <c r="N7" s="24"/>
+      <c r="O7" s="24"/>
+      <c r="P7" s="24"/>
+      <c r="Q7" s="24"/>
+      <c r="R7" s="24"/>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B8" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C8">
         <f t="shared" ref="C8:C68" si="1">IF(ISNUMBER(E8), IF(ISNUMBER(C7), C7+1, 1), "")</f>
@@ -6115,19 +6115,19 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G8))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>20</v>
       </c>
-      <c r="J8" s="39"/>
-      <c r="K8" s="39"/>
-      <c r="M8" s="37"/>
-      <c r="N8" s="37"/>
-      <c r="O8" s="37"/>
-      <c r="P8" s="37"/>
-      <c r="Q8" s="37"/>
-      <c r="R8" s="37"/>
+      <c r="J8" s="26"/>
+      <c r="K8" s="26"/>
+      <c r="M8" s="24"/>
+      <c r="N8" s="24"/>
+      <c r="O8" s="24"/>
+      <c r="P8" s="24"/>
+      <c r="Q8" s="24"/>
+      <c r="R8" s="24"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B9" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C9">
         <f t="shared" si="1"/>
@@ -6149,19 +6149,19 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G9))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>315</v>
       </c>
-      <c r="J9" s="39"/>
-      <c r="K9" s="39"/>
-      <c r="M9" s="37"/>
-      <c r="N9" s="37"/>
-      <c r="O9" s="37"/>
-      <c r="P9" s="37"/>
-      <c r="Q9" s="37"/>
-      <c r="R9" s="37"/>
+      <c r="J9" s="26"/>
+      <c r="K9" s="26"/>
+      <c r="M9" s="24"/>
+      <c r="N9" s="24"/>
+      <c r="O9" s="24"/>
+      <c r="P9" s="24"/>
+      <c r="Q9" s="24"/>
+      <c r="R9" s="24"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B10" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C10">
         <f t="shared" si="1"/>
@@ -6183,19 +6183,19 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G10))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>38</v>
       </c>
-      <c r="J10" s="39"/>
-      <c r="K10" s="39"/>
-      <c r="M10" s="37"/>
-      <c r="N10" s="37"/>
-      <c r="O10" s="37"/>
-      <c r="P10" s="37"/>
-      <c r="Q10" s="37"/>
-      <c r="R10" s="37"/>
+      <c r="J10" s="26"/>
+      <c r="K10" s="26"/>
+      <c r="M10" s="24"/>
+      <c r="N10" s="24"/>
+      <c r="O10" s="24"/>
+      <c r="P10" s="24"/>
+      <c r="Q10" s="24"/>
+      <c r="R10" s="24"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B11" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C11">
         <f t="shared" si="1"/>
@@ -6217,19 +6217,19 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G11))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>111.5</v>
       </c>
-      <c r="J11" s="39"/>
-      <c r="K11" s="39"/>
-      <c r="M11" s="37"/>
-      <c r="N11" s="37"/>
-      <c r="O11" s="37"/>
-      <c r="P11" s="37"/>
-      <c r="Q11" s="37"/>
-      <c r="R11" s="37"/>
+      <c r="J11" s="26"/>
+      <c r="K11" s="26"/>
+      <c r="M11" s="24"/>
+      <c r="N11" s="24"/>
+      <c r="O11" s="24"/>
+      <c r="P11" s="24"/>
+      <c r="Q11" s="24"/>
+      <c r="R11" s="24"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B12" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C12">
         <f t="shared" si="1"/>
@@ -6251,19 +6251,19 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G12))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>221.5</v>
       </c>
-      <c r="J12" s="39"/>
-      <c r="K12" s="39"/>
-      <c r="M12" s="37"/>
-      <c r="N12" s="37"/>
-      <c r="O12" s="37"/>
-      <c r="P12" s="37"/>
-      <c r="Q12" s="37"/>
-      <c r="R12" s="37"/>
+      <c r="J12" s="26"/>
+      <c r="K12" s="26"/>
+      <c r="M12" s="24"/>
+      <c r="N12" s="24"/>
+      <c r="O12" s="24"/>
+      <c r="P12" s="24"/>
+      <c r="Q12" s="24"/>
+      <c r="R12" s="24"/>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B13" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C13">
         <f t="shared" si="1"/>
@@ -6282,19 +6282,19 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G13))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>90</v>
       </c>
-      <c r="J13" s="39"/>
-      <c r="K13" s="39"/>
-      <c r="M13" s="37"/>
-      <c r="N13" s="37"/>
-      <c r="O13" s="37"/>
-      <c r="P13" s="37"/>
-      <c r="Q13" s="37"/>
-      <c r="R13" s="37"/>
+      <c r="J13" s="26"/>
+      <c r="K13" s="26"/>
+      <c r="M13" s="24"/>
+      <c r="N13" s="24"/>
+      <c r="O13" s="24"/>
+      <c r="P13" s="24"/>
+      <c r="Q13" s="24"/>
+      <c r="R13" s="24"/>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B14" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C14">
         <f t="shared" si="1"/>
@@ -6313,19 +6313,19 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G14))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>10</v>
       </c>
-      <c r="J14" s="39"/>
-      <c r="K14" s="39"/>
-      <c r="M14" s="37"/>
-      <c r="N14" s="37"/>
-      <c r="O14" s="37"/>
-      <c r="P14" s="37"/>
-      <c r="Q14" s="37"/>
-      <c r="R14" s="37"/>
+      <c r="J14" s="26"/>
+      <c r="K14" s="26"/>
+      <c r="M14" s="24"/>
+      <c r="N14" s="24"/>
+      <c r="O14" s="24"/>
+      <c r="P14" s="24"/>
+      <c r="Q14" s="24"/>
+      <c r="R14" s="24"/>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B15" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C15">
         <f t="shared" si="1"/>
@@ -6344,17 +6344,17 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G15))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>30</v>
       </c>
-      <c r="M15" s="37"/>
-      <c r="N15" s="37"/>
-      <c r="O15" s="37"/>
-      <c r="P15" s="37"/>
-      <c r="Q15" s="37"/>
-      <c r="R15" s="37"/>
+      <c r="M15" s="24"/>
+      <c r="N15" s="24"/>
+      <c r="O15" s="24"/>
+      <c r="P15" s="24"/>
+      <c r="Q15" s="24"/>
+      <c r="R15" s="24"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B16" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C16">
         <f t="shared" si="1"/>
@@ -6373,17 +6373,17 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G16))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>5</v>
       </c>
-      <c r="M16" s="37"/>
-      <c r="N16" s="37"/>
-      <c r="O16" s="37"/>
-      <c r="P16" s="37"/>
-      <c r="Q16" s="37"/>
-      <c r="R16" s="37"/>
+      <c r="M16" s="24"/>
+      <c r="N16" s="24"/>
+      <c r="O16" s="24"/>
+      <c r="P16" s="24"/>
+      <c r="Q16" s="24"/>
+      <c r="R16" s="24"/>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B17" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C17">
         <f t="shared" si="1"/>
@@ -6402,17 +6402,17 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G17))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>110</v>
       </c>
-      <c r="M17" s="37"/>
-      <c r="N17" s="37"/>
-      <c r="O17" s="37"/>
-      <c r="P17" s="37"/>
-      <c r="Q17" s="37"/>
-      <c r="R17" s="37"/>
+      <c r="M17" s="24"/>
+      <c r="N17" s="24"/>
+      <c r="O17" s="24"/>
+      <c r="P17" s="24"/>
+      <c r="Q17" s="24"/>
+      <c r="R17" s="24"/>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B18" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C18">
         <f t="shared" si="1"/>
@@ -6431,17 +6431,17 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G18))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>220</v>
       </c>
-      <c r="M18" s="37"/>
-      <c r="N18" s="37"/>
-      <c r="O18" s="37"/>
-      <c r="P18" s="37"/>
-      <c r="Q18" s="37"/>
-      <c r="R18" s="37"/>
+      <c r="M18" s="24"/>
+      <c r="N18" s="24"/>
+      <c r="O18" s="24"/>
+      <c r="P18" s="24"/>
+      <c r="Q18" s="24"/>
+      <c r="R18" s="24"/>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B19" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C19">
         <f t="shared" si="1"/>
@@ -6460,17 +6460,17 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G19))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>20</v>
       </c>
-      <c r="M19" s="37"/>
-      <c r="N19" s="37"/>
-      <c r="O19" s="37"/>
-      <c r="P19" s="37"/>
-      <c r="Q19" s="37"/>
-      <c r="R19" s="37"/>
+      <c r="M19" s="24"/>
+      <c r="N19" s="24"/>
+      <c r="O19" s="24"/>
+      <c r="P19" s="24"/>
+      <c r="Q19" s="24"/>
+      <c r="R19" s="24"/>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B20" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C20">
         <f t="shared" si="1"/>
@@ -6489,12 +6489,12 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G20))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>48</v>
       </c>
-      <c r="M20" s="37"/>
-      <c r="N20" s="37"/>
-      <c r="O20" s="37"/>
-      <c r="P20" s="37"/>
-      <c r="Q20" s="37"/>
-      <c r="R20" s="37"/>
+      <c r="M20" s="24"/>
+      <c r="N20" s="24"/>
+      <c r="O20" s="24"/>
+      <c r="P20" s="24"/>
+      <c r="Q20" s="24"/>
+      <c r="R20" s="24"/>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B21" s="18" t="str">
@@ -6521,12 +6521,12 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G21))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>38</v>
       </c>
-      <c r="M21" s="37"/>
-      <c r="N21" s="37"/>
-      <c r="O21" s="37"/>
-      <c r="P21" s="37"/>
-      <c r="Q21" s="37"/>
-      <c r="R21" s="37"/>
+      <c r="M21" s="24"/>
+      <c r="N21" s="24"/>
+      <c r="O21" s="24"/>
+      <c r="P21" s="24"/>
+      <c r="Q21" s="24"/>
+      <c r="R21" s="24"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B22" s="18" t="str">
@@ -6553,12 +6553,12 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G22))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>32.5</v>
       </c>
-      <c r="M22" s="37"/>
-      <c r="N22" s="37"/>
-      <c r="O22" s="37"/>
-      <c r="P22" s="37"/>
-      <c r="Q22" s="37"/>
-      <c r="R22" s="37"/>
+      <c r="M22" s="24"/>
+      <c r="N22" s="24"/>
+      <c r="O22" s="24"/>
+      <c r="P22" s="24"/>
+      <c r="Q22" s="24"/>
+      <c r="R22" s="24"/>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B23" s="18" t="str">
@@ -6599,14 +6599,14 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G24))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M24" s="33" t="s">
+      <c r="M24" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="N24" s="46"/>
-      <c r="O24" s="46"/>
-      <c r="P24" s="46"/>
-      <c r="Q24" s="46"/>
-      <c r="R24" s="46"/>
+      <c r="N24" s="40"/>
+      <c r="O24" s="40"/>
+      <c r="P24" s="40"/>
+      <c r="Q24" s="40"/>
+      <c r="R24" s="40"/>
     </row>
     <row r="25" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B25" s="18" t="str">
@@ -6621,12 +6621,12 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G25))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M25" s="38"/>
-      <c r="N25" s="38"/>
-      <c r="O25" s="38"/>
-      <c r="P25" s="38"/>
-      <c r="Q25" s="38"/>
-      <c r="R25" s="38"/>
+      <c r="M25" s="25"/>
+      <c r="N25" s="25"/>
+      <c r="O25" s="25"/>
+      <c r="P25" s="25"/>
+      <c r="Q25" s="25"/>
+      <c r="R25" s="25"/>
     </row>
     <row r="26" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="18" t="str">
@@ -6647,12 +6647,12 @@
       <c r="N26" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="O26" s="32" t="s">
+      <c r="O26" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="P26" s="32"/>
-      <c r="Q26" s="32"/>
-      <c r="R26" s="32"/>
+      <c r="P26" s="39"/>
+      <c r="Q26" s="39"/>
+      <c r="R26" s="39"/>
     </row>
     <row r="27" spans="2:18" ht="45" x14ac:dyDescent="0.25">
       <c r="B27" s="18" t="str">
@@ -6673,10 +6673,10 @@
       <c r="N27" s="15">
         <v>7781</v>
       </c>
-      <c r="O27" s="40"/>
-      <c r="P27" s="41"/>
-      <c r="Q27" s="41"/>
-      <c r="R27" s="42"/>
+      <c r="O27" s="41"/>
+      <c r="P27" s="42"/>
+      <c r="Q27" s="42"/>
+      <c r="R27" s="43"/>
     </row>
     <row r="28" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B28" s="18" t="str">
@@ -6693,10 +6693,10 @@
       </c>
       <c r="M28" s="13"/>
       <c r="N28" s="15"/>
-      <c r="O28" s="40"/>
-      <c r="P28" s="41"/>
-      <c r="Q28" s="41"/>
-      <c r="R28" s="42"/>
+      <c r="O28" s="41"/>
+      <c r="P28" s="42"/>
+      <c r="Q28" s="42"/>
+      <c r="R28" s="43"/>
     </row>
     <row r="29" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B29" s="18" t="str">
@@ -6713,10 +6713,10 @@
       </c>
       <c r="M29" s="13"/>
       <c r="N29" s="15"/>
-      <c r="O29" s="40"/>
-      <c r="P29" s="41"/>
-      <c r="Q29" s="41"/>
-      <c r="R29" s="42"/>
+      <c r="O29" s="41"/>
+      <c r="P29" s="42"/>
+      <c r="Q29" s="42"/>
+      <c r="R29" s="43"/>
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B30" s="18" t="str">
@@ -6733,10 +6733,10 @@
       </c>
       <c r="M30" s="13"/>
       <c r="N30" s="15"/>
-      <c r="O30" s="40"/>
-      <c r="P30" s="41"/>
-      <c r="Q30" s="41"/>
-      <c r="R30" s="42"/>
+      <c r="O30" s="41"/>
+      <c r="P30" s="42"/>
+      <c r="Q30" s="42"/>
+      <c r="R30" s="43"/>
     </row>
     <row r="31" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B31" s="18" t="str">
@@ -6753,10 +6753,10 @@
       </c>
       <c r="M31" s="13"/>
       <c r="N31" s="15"/>
-      <c r="O31" s="40"/>
-      <c r="P31" s="41"/>
-      <c r="Q31" s="41"/>
-      <c r="R31" s="42"/>
+      <c r="O31" s="41"/>
+      <c r="P31" s="42"/>
+      <c r="Q31" s="42"/>
+      <c r="R31" s="43"/>
     </row>
     <row r="32" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B32" s="18" t="str">
@@ -6773,10 +6773,10 @@
       </c>
       <c r="M32" s="13"/>
       <c r="N32" s="15"/>
-      <c r="O32" s="40"/>
-      <c r="P32" s="41"/>
-      <c r="Q32" s="41"/>
-      <c r="R32" s="42"/>
+      <c r="O32" s="41"/>
+      <c r="P32" s="42"/>
+      <c r="Q32" s="42"/>
+      <c r="R32" s="43"/>
     </row>
     <row r="33" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B33" s="18" t="str">
@@ -6793,10 +6793,10 @@
       </c>
       <c r="M33" s="13"/>
       <c r="N33" s="15"/>
-      <c r="O33" s="40"/>
-      <c r="P33" s="41"/>
-      <c r="Q33" s="41"/>
-      <c r="R33" s="42"/>
+      <c r="O33" s="41"/>
+      <c r="P33" s="42"/>
+      <c r="Q33" s="42"/>
+      <c r="R33" s="43"/>
     </row>
     <row r="34" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B34" s="18" t="str">
@@ -6813,10 +6813,10 @@
       </c>
       <c r="M34" s="13"/>
       <c r="N34" s="15"/>
-      <c r="O34" s="40"/>
-      <c r="P34" s="41"/>
-      <c r="Q34" s="41"/>
-      <c r="R34" s="42"/>
+      <c r="O34" s="41"/>
+      <c r="P34" s="42"/>
+      <c r="Q34" s="42"/>
+      <c r="R34" s="43"/>
     </row>
     <row r="35" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B35" s="18" t="str">
@@ -6833,10 +6833,10 @@
       </c>
       <c r="M35" s="13"/>
       <c r="N35" s="15"/>
-      <c r="O35" s="40"/>
-      <c r="P35" s="41"/>
-      <c r="Q35" s="41"/>
-      <c r="R35" s="42"/>
+      <c r="O35" s="41"/>
+      <c r="P35" s="42"/>
+      <c r="Q35" s="42"/>
+      <c r="R35" s="43"/>
     </row>
     <row r="36" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B36" s="18" t="str">
@@ -6853,10 +6853,10 @@
       </c>
       <c r="M36" s="13"/>
       <c r="N36" s="15"/>
-      <c r="O36" s="40"/>
-      <c r="P36" s="41"/>
-      <c r="Q36" s="41"/>
-      <c r="R36" s="42"/>
+      <c r="O36" s="41"/>
+      <c r="P36" s="42"/>
+      <c r="Q36" s="42"/>
+      <c r="R36" s="43"/>
     </row>
     <row r="37" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B37" s="18" t="str">
@@ -6873,10 +6873,10 @@
       </c>
       <c r="M37" s="13"/>
       <c r="N37" s="15"/>
-      <c r="O37" s="40"/>
-      <c r="P37" s="41"/>
-      <c r="Q37" s="41"/>
-      <c r="R37" s="42"/>
+      <c r="O37" s="41"/>
+      <c r="P37" s="42"/>
+      <c r="Q37" s="42"/>
+      <c r="R37" s="43"/>
     </row>
     <row r="38" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B38" s="18" t="str">
@@ -6893,10 +6893,10 @@
       </c>
       <c r="M38" s="13"/>
       <c r="N38" s="15"/>
-      <c r="O38" s="40"/>
-      <c r="P38" s="41"/>
-      <c r="Q38" s="41"/>
-      <c r="R38" s="42"/>
+      <c r="O38" s="41"/>
+      <c r="P38" s="42"/>
+      <c r="Q38" s="42"/>
+      <c r="R38" s="43"/>
     </row>
     <row r="39" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B39" s="18" t="str">
@@ -6913,10 +6913,10 @@
       </c>
       <c r="M39" s="13"/>
       <c r="N39" s="15"/>
-      <c r="O39" s="40"/>
-      <c r="P39" s="41"/>
-      <c r="Q39" s="41"/>
-      <c r="R39" s="42"/>
+      <c r="O39" s="41"/>
+      <c r="P39" s="42"/>
+      <c r="Q39" s="42"/>
+      <c r="R39" s="43"/>
     </row>
     <row r="40" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B40" s="18" t="str">
@@ -6936,10 +6936,10 @@
       </c>
       <c r="M40" s="13"/>
       <c r="N40" s="15"/>
-      <c r="O40" s="40"/>
-      <c r="P40" s="41"/>
-      <c r="Q40" s="41"/>
-      <c r="R40" s="42"/>
+      <c r="O40" s="41"/>
+      <c r="P40" s="42"/>
+      <c r="Q40" s="42"/>
+      <c r="R40" s="43"/>
     </row>
     <row r="41" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B41" s="18" t="str">
@@ -6956,10 +6956,10 @@
       </c>
       <c r="M41" s="13"/>
       <c r="N41" s="15"/>
-      <c r="O41" s="40"/>
-      <c r="P41" s="41"/>
-      <c r="Q41" s="41"/>
-      <c r="R41" s="42"/>
+      <c r="O41" s="41"/>
+      <c r="P41" s="42"/>
+      <c r="Q41" s="42"/>
+      <c r="R41" s="43"/>
     </row>
     <row r="42" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B42" s="18" t="str">
@@ -6976,10 +6976,10 @@
       </c>
       <c r="M42" s="13"/>
       <c r="N42" s="15"/>
-      <c r="O42" s="40"/>
-      <c r="P42" s="41"/>
-      <c r="Q42" s="41"/>
-      <c r="R42" s="42"/>
+      <c r="O42" s="41"/>
+      <c r="P42" s="42"/>
+      <c r="Q42" s="42"/>
+      <c r="R42" s="43"/>
     </row>
     <row r="43" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B43" s="18" t="str">
@@ -6996,10 +6996,10 @@
       </c>
       <c r="M43" s="13"/>
       <c r="N43" s="15"/>
-      <c r="O43" s="40"/>
-      <c r="P43" s="41"/>
-      <c r="Q43" s="41"/>
-      <c r="R43" s="42"/>
+      <c r="O43" s="41"/>
+      <c r="P43" s="42"/>
+      <c r="Q43" s="42"/>
+      <c r="R43" s="43"/>
     </row>
     <row r="44" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B44" s="18" t="str">
@@ -7016,10 +7016,10 @@
       </c>
       <c r="M44" s="13"/>
       <c r="N44" s="15"/>
-      <c r="O44" s="40"/>
-      <c r="P44" s="41"/>
-      <c r="Q44" s="41"/>
-      <c r="R44" s="42"/>
+      <c r="O44" s="41"/>
+      <c r="P44" s="42"/>
+      <c r="Q44" s="42"/>
+      <c r="R44" s="43"/>
     </row>
     <row r="45" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B45" s="18" t="str">
@@ -7849,32 +7849,32 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="C2:H2"/>
-    <mergeCell ref="M2:R2"/>
-    <mergeCell ref="M3:R3"/>
-    <mergeCell ref="M4:R22"/>
-    <mergeCell ref="J5:K14"/>
-    <mergeCell ref="M24:R24"/>
-    <mergeCell ref="M25:R25"/>
-    <mergeCell ref="O26:R26"/>
-    <mergeCell ref="O27:R27"/>
-    <mergeCell ref="O28:R28"/>
-    <mergeCell ref="O29:R29"/>
-    <mergeCell ref="O30:R30"/>
-    <mergeCell ref="O31:R31"/>
-    <mergeCell ref="O32:R32"/>
-    <mergeCell ref="O33:R33"/>
-    <mergeCell ref="O34:R34"/>
-    <mergeCell ref="O35:R35"/>
-    <mergeCell ref="O36:R36"/>
-    <mergeCell ref="O37:R37"/>
-    <mergeCell ref="O38:R38"/>
     <mergeCell ref="O44:R44"/>
     <mergeCell ref="O39:R39"/>
     <mergeCell ref="O40:R40"/>
     <mergeCell ref="O41:R41"/>
     <mergeCell ref="O42:R42"/>
     <mergeCell ref="O43:R43"/>
+    <mergeCell ref="O34:R34"/>
+    <mergeCell ref="O35:R35"/>
+    <mergeCell ref="O36:R36"/>
+    <mergeCell ref="O37:R37"/>
+    <mergeCell ref="O38:R38"/>
+    <mergeCell ref="O29:R29"/>
+    <mergeCell ref="O30:R30"/>
+    <mergeCell ref="O31:R31"/>
+    <mergeCell ref="O32:R32"/>
+    <mergeCell ref="O33:R33"/>
+    <mergeCell ref="M24:R24"/>
+    <mergeCell ref="M25:R25"/>
+    <mergeCell ref="O26:R26"/>
+    <mergeCell ref="O27:R27"/>
+    <mergeCell ref="O28:R28"/>
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="M2:R2"/>
+    <mergeCell ref="M3:R3"/>
+    <mergeCell ref="M4:R22"/>
+    <mergeCell ref="J5:K14"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B103">
     <cfRule type="expression" dxfId="9" priority="1">
@@ -7912,23 +7912,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="C2" s="35" t="s">
+      <c r="C2" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="D2" s="35"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
       <c r="L2" s="8"/>
-      <c r="M2" s="35" t="s">
+      <c r="M2" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="36"/>
-      <c r="O2" s="36"/>
-      <c r="P2" s="36"/>
-      <c r="Q2" s="36"/>
-      <c r="R2" s="36"/>
+      <c r="N2" s="23"/>
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
+      <c r="R2" s="23"/>
     </row>
     <row r="3" spans="2:18" ht="26.25" x14ac:dyDescent="0.4">
       <c r="G3" t="s">
@@ -7941,14 +7941,14 @@
         <f>SUM(Tabla112[Importa])</f>
         <v>1288.5</v>
       </c>
-      <c r="M3" s="38" t="s">
+      <c r="M3" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="38"/>
-      <c r="O3" s="38"/>
-      <c r="P3" s="38"/>
-      <c r="Q3" s="38"/>
-      <c r="R3" s="38"/>
+      <c r="N3" s="25"/>
+      <c r="O3" s="25"/>
+      <c r="P3" s="25"/>
+      <c r="Q3" s="25"/>
+      <c r="R3" s="25"/>
     </row>
     <row r="4" spans="2:18" ht="33.75" x14ac:dyDescent="0.5">
       <c r="B4" s="17" t="s">
@@ -7979,19 +7979,19 @@
         <f>COUNTIF(C5:C103,"&gt;0")</f>
         <v>13</v>
       </c>
-      <c r="M4" s="37" t="s">
+      <c r="M4" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="N4" s="37"/>
-      <c r="O4" s="37"/>
-      <c r="P4" s="37"/>
-      <c r="Q4" s="37"/>
-      <c r="R4" s="37"/>
+      <c r="N4" s="24"/>
+      <c r="O4" s="24"/>
+      <c r="P4" s="24"/>
+      <c r="Q4" s="24"/>
+      <c r="R4" s="24"/>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B5" s="18">
         <f ca="1">IF(Tabla112[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C5">
         <f t="shared" ref="C5:C68" si="0">IF(ISNUMBER(E5), IF(ISNUMBER(C4), C4+1, 1), "")</f>
@@ -8010,21 +8010,21 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G5))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>20</v>
       </c>
-      <c r="J5" s="39" t="s">
+      <c r="J5" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="K5" s="39"/>
-      <c r="M5" s="37"/>
-      <c r="N5" s="37"/>
-      <c r="O5" s="37"/>
-      <c r="P5" s="37"/>
-      <c r="Q5" s="37"/>
-      <c r="R5" s="37"/>
+      <c r="K5" s="26"/>
+      <c r="M5" s="24"/>
+      <c r="N5" s="24"/>
+      <c r="O5" s="24"/>
+      <c r="P5" s="24"/>
+      <c r="Q5" s="24"/>
+      <c r="R5" s="24"/>
     </row>
     <row r="6" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C6">
         <f t="shared" si="0"/>
@@ -8043,19 +8043,19 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G6))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>40</v>
       </c>
-      <c r="J6" s="39"/>
-      <c r="K6" s="39"/>
-      <c r="M6" s="37"/>
-      <c r="N6" s="37"/>
-      <c r="O6" s="37"/>
-      <c r="P6" s="37"/>
-      <c r="Q6" s="37"/>
-      <c r="R6" s="37"/>
+      <c r="J6" s="26"/>
+      <c r="K6" s="26"/>
+      <c r="M6" s="24"/>
+      <c r="N6" s="24"/>
+      <c r="O6" s="24"/>
+      <c r="P6" s="24"/>
+      <c r="Q6" s="24"/>
+      <c r="R6" s="24"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B7" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
@@ -8077,19 +8077,19 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G7))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>108</v>
       </c>
-      <c r="J7" s="39"/>
-      <c r="K7" s="39"/>
-      <c r="M7" s="37"/>
-      <c r="N7" s="37"/>
-      <c r="O7" s="37"/>
-      <c r="P7" s="37"/>
-      <c r="Q7" s="37"/>
-      <c r="R7" s="37"/>
+      <c r="J7" s="26"/>
+      <c r="K7" s="26"/>
+      <c r="M7" s="24"/>
+      <c r="N7" s="24"/>
+      <c r="O7" s="24"/>
+      <c r="P7" s="24"/>
+      <c r="Q7" s="24"/>
+      <c r="R7" s="24"/>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B8" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C8">
         <f t="shared" si="0"/>
@@ -8111,19 +8111,19 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G8))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>31.5</v>
       </c>
-      <c r="J8" s="39"/>
-      <c r="K8" s="39"/>
-      <c r="M8" s="37"/>
-      <c r="N8" s="37"/>
-      <c r="O8" s="37"/>
-      <c r="P8" s="37"/>
-      <c r="Q8" s="37"/>
-      <c r="R8" s="37"/>
+      <c r="J8" s="26"/>
+      <c r="K8" s="26"/>
+      <c r="M8" s="24"/>
+      <c r="N8" s="24"/>
+      <c r="O8" s="24"/>
+      <c r="P8" s="24"/>
+      <c r="Q8" s="24"/>
+      <c r="R8" s="24"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B9" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C9">
         <f t="shared" si="0"/>
@@ -8145,19 +8145,19 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G9))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>58</v>
       </c>
-      <c r="J9" s="39"/>
-      <c r="K9" s="39"/>
-      <c r="M9" s="37"/>
-      <c r="N9" s="37"/>
-      <c r="O9" s="37"/>
-      <c r="P9" s="37"/>
-      <c r="Q9" s="37"/>
-      <c r="R9" s="37"/>
+      <c r="J9" s="26"/>
+      <c r="K9" s="26"/>
+      <c r="M9" s="24"/>
+      <c r="N9" s="24"/>
+      <c r="O9" s="24"/>
+      <c r="P9" s="24"/>
+      <c r="Q9" s="24"/>
+      <c r="R9" s="24"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B10" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C10">
         <f t="shared" si="0"/>
@@ -8176,19 +8176,19 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G10))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>20</v>
       </c>
-      <c r="J10" s="39"/>
-      <c r="K10" s="39"/>
-      <c r="M10" s="37"/>
-      <c r="N10" s="37"/>
-      <c r="O10" s="37"/>
-      <c r="P10" s="37"/>
-      <c r="Q10" s="37"/>
-      <c r="R10" s="37"/>
+      <c r="J10" s="26"/>
+      <c r="K10" s="26"/>
+      <c r="M10" s="24"/>
+      <c r="N10" s="24"/>
+      <c r="O10" s="24"/>
+      <c r="P10" s="24"/>
+      <c r="Q10" s="24"/>
+      <c r="R10" s="24"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B11" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C11">
         <f t="shared" si="0"/>
@@ -8207,19 +8207,19 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G11))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>180</v>
       </c>
-      <c r="J11" s="39"/>
-      <c r="K11" s="39"/>
-      <c r="M11" s="37"/>
-      <c r="N11" s="37"/>
-      <c r="O11" s="37"/>
-      <c r="P11" s="37"/>
-      <c r="Q11" s="37"/>
-      <c r="R11" s="37"/>
+      <c r="J11" s="26"/>
+      <c r="K11" s="26"/>
+      <c r="M11" s="24"/>
+      <c r="N11" s="24"/>
+      <c r="O11" s="24"/>
+      <c r="P11" s="24"/>
+      <c r="Q11" s="24"/>
+      <c r="R11" s="24"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B12" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C12">
         <f t="shared" si="0"/>
@@ -8238,19 +8238,19 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G12))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>10</v>
       </c>
-      <c r="J12" s="39"/>
-      <c r="K12" s="39"/>
-      <c r="M12" s="37"/>
-      <c r="N12" s="37"/>
-      <c r="O12" s="37"/>
-      <c r="P12" s="37"/>
-      <c r="Q12" s="37"/>
-      <c r="R12" s="37"/>
+      <c r="J12" s="26"/>
+      <c r="K12" s="26"/>
+      <c r="M12" s="24"/>
+      <c r="N12" s="24"/>
+      <c r="O12" s="24"/>
+      <c r="P12" s="24"/>
+      <c r="Q12" s="24"/>
+      <c r="R12" s="24"/>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B13" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C13">
         <f t="shared" si="0"/>
@@ -8269,19 +8269,19 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G13))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>150</v>
       </c>
-      <c r="J13" s="39"/>
-      <c r="K13" s="39"/>
-      <c r="M13" s="37"/>
-      <c r="N13" s="37"/>
-      <c r="O13" s="37"/>
-      <c r="P13" s="37"/>
-      <c r="Q13" s="37"/>
-      <c r="R13" s="37"/>
+      <c r="J13" s="26"/>
+      <c r="K13" s="26"/>
+      <c r="M13" s="24"/>
+      <c r="N13" s="24"/>
+      <c r="O13" s="24"/>
+      <c r="P13" s="24"/>
+      <c r="Q13" s="24"/>
+      <c r="R13" s="24"/>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B14" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C14">
         <f t="shared" si="0"/>
@@ -8300,19 +8300,19 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G14))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>32</v>
       </c>
-      <c r="J14" s="39"/>
-      <c r="K14" s="39"/>
-      <c r="M14" s="37"/>
-      <c r="N14" s="37"/>
-      <c r="O14" s="37"/>
-      <c r="P14" s="37"/>
-      <c r="Q14" s="37"/>
-      <c r="R14" s="37"/>
+      <c r="J14" s="26"/>
+      <c r="K14" s="26"/>
+      <c r="M14" s="24"/>
+      <c r="N14" s="24"/>
+      <c r="O14" s="24"/>
+      <c r="P14" s="24"/>
+      <c r="Q14" s="24"/>
+      <c r="R14" s="24"/>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B15" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C15">
         <f t="shared" si="0"/>
@@ -8331,17 +8331,17 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G15))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>135</v>
       </c>
-      <c r="M15" s="37"/>
-      <c r="N15" s="37"/>
-      <c r="O15" s="37"/>
-      <c r="P15" s="37"/>
-      <c r="Q15" s="37"/>
-      <c r="R15" s="37"/>
+      <c r="M15" s="24"/>
+      <c r="N15" s="24"/>
+      <c r="O15" s="24"/>
+      <c r="P15" s="24"/>
+      <c r="Q15" s="24"/>
+      <c r="R15" s="24"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B16" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C16">
         <f t="shared" si="0"/>
@@ -8363,17 +8363,17 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G16))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>342</v>
       </c>
-      <c r="M16" s="37"/>
-      <c r="N16" s="37"/>
-      <c r="O16" s="37"/>
-      <c r="P16" s="37"/>
-      <c r="Q16" s="37"/>
-      <c r="R16" s="37"/>
+      <c r="M16" s="24"/>
+      <c r="N16" s="24"/>
+      <c r="O16" s="24"/>
+      <c r="P16" s="24"/>
+      <c r="Q16" s="24"/>
+      <c r="R16" s="24"/>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B17" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C17">
         <f t="shared" si="0"/>
@@ -8395,17 +8395,17 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G17))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>162</v>
       </c>
-      <c r="M17" s="37"/>
-      <c r="N17" s="37"/>
-      <c r="O17" s="37"/>
-      <c r="P17" s="37"/>
-      <c r="Q17" s="37"/>
-      <c r="R17" s="37"/>
+      <c r="M17" s="24"/>
+      <c r="N17" s="24"/>
+      <c r="O17" s="24"/>
+      <c r="P17" s="24"/>
+      <c r="Q17" s="24"/>
+      <c r="R17" s="24"/>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B18" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C18" t="str">
         <f t="shared" si="0"/>
@@ -8415,17 +8415,17 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G18))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M18" s="37"/>
-      <c r="N18" s="37"/>
-      <c r="O18" s="37"/>
-      <c r="P18" s="37"/>
-      <c r="Q18" s="37"/>
-      <c r="R18" s="37"/>
+      <c r="M18" s="24"/>
+      <c r="N18" s="24"/>
+      <c r="O18" s="24"/>
+      <c r="P18" s="24"/>
+      <c r="Q18" s="24"/>
+      <c r="R18" s="24"/>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B19" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C19" t="str">
         <f t="shared" si="0"/>
@@ -8435,17 +8435,17 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G19))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M19" s="37"/>
-      <c r="N19" s="37"/>
-      <c r="O19" s="37"/>
-      <c r="P19" s="37"/>
-      <c r="Q19" s="37"/>
-      <c r="R19" s="37"/>
+      <c r="M19" s="24"/>
+      <c r="N19" s="24"/>
+      <c r="O19" s="24"/>
+      <c r="P19" s="24"/>
+      <c r="Q19" s="24"/>
+      <c r="R19" s="24"/>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B20" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C20" t="str">
         <f t="shared" si="0"/>
@@ -8455,12 +8455,12 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G20))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M20" s="37"/>
-      <c r="N20" s="37"/>
-      <c r="O20" s="37"/>
-      <c r="P20" s="37"/>
-      <c r="Q20" s="37"/>
-      <c r="R20" s="37"/>
+      <c r="M20" s="24"/>
+      <c r="N20" s="24"/>
+      <c r="O20" s="24"/>
+      <c r="P20" s="24"/>
+      <c r="Q20" s="24"/>
+      <c r="R20" s="24"/>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B21" s="18" t="str">
@@ -8475,12 +8475,12 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G21))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M21" s="37"/>
-      <c r="N21" s="37"/>
-      <c r="O21" s="37"/>
-      <c r="P21" s="37"/>
-      <c r="Q21" s="37"/>
-      <c r="R21" s="37"/>
+      <c r="M21" s="24"/>
+      <c r="N21" s="24"/>
+      <c r="O21" s="24"/>
+      <c r="P21" s="24"/>
+      <c r="Q21" s="24"/>
+      <c r="R21" s="24"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B22" s="18" t="str">
@@ -8495,12 +8495,12 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G22))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M22" s="37"/>
-      <c r="N22" s="37"/>
-      <c r="O22" s="37"/>
-      <c r="P22" s="37"/>
-      <c r="Q22" s="37"/>
-      <c r="R22" s="37"/>
+      <c r="M22" s="24"/>
+      <c r="N22" s="24"/>
+      <c r="O22" s="24"/>
+      <c r="P22" s="24"/>
+      <c r="Q22" s="24"/>
+      <c r="R22" s="24"/>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B23" s="18" t="str">
@@ -8529,14 +8529,14 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G24))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M24" s="33" t="s">
+      <c r="M24" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="N24" s="46"/>
-      <c r="O24" s="46"/>
-      <c r="P24" s="46"/>
-      <c r="Q24" s="46"/>
-      <c r="R24" s="46"/>
+      <c r="N24" s="40"/>
+      <c r="O24" s="40"/>
+      <c r="P24" s="40"/>
+      <c r="Q24" s="40"/>
+      <c r="R24" s="40"/>
     </row>
     <row r="25" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="18" t="str">
@@ -8551,12 +8551,12 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G25))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M25" s="38"/>
-      <c r="N25" s="38"/>
-      <c r="O25" s="38"/>
-      <c r="P25" s="38"/>
-      <c r="Q25" s="38"/>
-      <c r="R25" s="38"/>
+      <c r="M25" s="25"/>
+      <c r="N25" s="25"/>
+      <c r="O25" s="25"/>
+      <c r="P25" s="25"/>
+      <c r="Q25" s="25"/>
+      <c r="R25" s="25"/>
     </row>
     <row r="26" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="18" t="str">
@@ -8577,12 +8577,12 @@
       <c r="N26" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="O26" s="32" t="s">
+      <c r="O26" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="P26" s="32"/>
-      <c r="Q26" s="32"/>
-      <c r="R26" s="32"/>
+      <c r="P26" s="39"/>
+      <c r="Q26" s="39"/>
+      <c r="R26" s="39"/>
     </row>
     <row r="27" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="18" t="str">
@@ -8603,10 +8603,10 @@
       <c r="N27" s="15">
         <v>69</v>
       </c>
-      <c r="O27" s="40"/>
-      <c r="P27" s="41"/>
-      <c r="Q27" s="41"/>
-      <c r="R27" s="42"/>
+      <c r="O27" s="41"/>
+      <c r="P27" s="42"/>
+      <c r="Q27" s="42"/>
+      <c r="R27" s="43"/>
     </row>
     <row r="28" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="18" t="str">
@@ -8623,10 +8623,10 @@
       </c>
       <c r="M28" s="13"/>
       <c r="N28" s="15"/>
-      <c r="O28" s="40"/>
-      <c r="P28" s="41"/>
-      <c r="Q28" s="41"/>
-      <c r="R28" s="42"/>
+      <c r="O28" s="41"/>
+      <c r="P28" s="42"/>
+      <c r="Q28" s="42"/>
+      <c r="R28" s="43"/>
     </row>
     <row r="29" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="18" t="str">
@@ -8643,10 +8643,10 @@
       </c>
       <c r="M29" s="13"/>
       <c r="N29" s="15"/>
-      <c r="O29" s="40"/>
-      <c r="P29" s="41"/>
-      <c r="Q29" s="41"/>
-      <c r="R29" s="42"/>
+      <c r="O29" s="41"/>
+      <c r="P29" s="42"/>
+      <c r="Q29" s="42"/>
+      <c r="R29" s="43"/>
     </row>
     <row r="30" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="18" t="str">
@@ -8663,10 +8663,10 @@
       </c>
       <c r="M30" s="13"/>
       <c r="N30" s="15"/>
-      <c r="O30" s="40"/>
-      <c r="P30" s="41"/>
-      <c r="Q30" s="41"/>
-      <c r="R30" s="42"/>
+      <c r="O30" s="41"/>
+      <c r="P30" s="42"/>
+      <c r="Q30" s="42"/>
+      <c r="R30" s="43"/>
     </row>
     <row r="31" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="18" t="str">
@@ -8683,10 +8683,10 @@
       </c>
       <c r="M31" s="13"/>
       <c r="N31" s="15"/>
-      <c r="O31" s="40"/>
-      <c r="P31" s="41"/>
-      <c r="Q31" s="41"/>
-      <c r="R31" s="42"/>
+      <c r="O31" s="41"/>
+      <c r="P31" s="42"/>
+      <c r="Q31" s="42"/>
+      <c r="R31" s="43"/>
     </row>
     <row r="32" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="18" t="str">
@@ -8703,10 +8703,10 @@
       </c>
       <c r="M32" s="13"/>
       <c r="N32" s="15"/>
-      <c r="O32" s="40"/>
-      <c r="P32" s="41"/>
-      <c r="Q32" s="41"/>
-      <c r="R32" s="42"/>
+      <c r="O32" s="41"/>
+      <c r="P32" s="42"/>
+      <c r="Q32" s="42"/>
+      <c r="R32" s="43"/>
     </row>
     <row r="33" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="18" t="str">
@@ -8723,10 +8723,10 @@
       </c>
       <c r="M33" s="13"/>
       <c r="N33" s="15"/>
-      <c r="O33" s="40"/>
-      <c r="P33" s="41"/>
-      <c r="Q33" s="41"/>
-      <c r="R33" s="42"/>
+      <c r="O33" s="41"/>
+      <c r="P33" s="42"/>
+      <c r="Q33" s="42"/>
+      <c r="R33" s="43"/>
     </row>
     <row r="34" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="18" t="str">
@@ -8743,10 +8743,10 @@
       </c>
       <c r="M34" s="13"/>
       <c r="N34" s="15"/>
-      <c r="O34" s="40"/>
-      <c r="P34" s="41"/>
-      <c r="Q34" s="41"/>
-      <c r="R34" s="42"/>
+      <c r="O34" s="41"/>
+      <c r="P34" s="42"/>
+      <c r="Q34" s="42"/>
+      <c r="R34" s="43"/>
     </row>
     <row r="35" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="18" t="str">
@@ -8763,10 +8763,10 @@
       </c>
       <c r="M35" s="13"/>
       <c r="N35" s="15"/>
-      <c r="O35" s="40"/>
-      <c r="P35" s="41"/>
-      <c r="Q35" s="41"/>
-      <c r="R35" s="42"/>
+      <c r="O35" s="41"/>
+      <c r="P35" s="42"/>
+      <c r="Q35" s="42"/>
+      <c r="R35" s="43"/>
     </row>
     <row r="36" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="18" t="str">
@@ -8783,10 +8783,10 @@
       </c>
       <c r="M36" s="13"/>
       <c r="N36" s="15"/>
-      <c r="O36" s="40"/>
-      <c r="P36" s="41"/>
-      <c r="Q36" s="41"/>
-      <c r="R36" s="42"/>
+      <c r="O36" s="41"/>
+      <c r="P36" s="42"/>
+      <c r="Q36" s="42"/>
+      <c r="R36" s="43"/>
     </row>
     <row r="37" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="18" t="str">
@@ -8803,10 +8803,10 @@
       </c>
       <c r="M37" s="13"/>
       <c r="N37" s="15"/>
-      <c r="O37" s="40"/>
-      <c r="P37" s="41"/>
-      <c r="Q37" s="41"/>
-      <c r="R37" s="42"/>
+      <c r="O37" s="41"/>
+      <c r="P37" s="42"/>
+      <c r="Q37" s="42"/>
+      <c r="R37" s="43"/>
     </row>
     <row r="38" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="18" t="str">
@@ -8823,10 +8823,10 @@
       </c>
       <c r="M38" s="13"/>
       <c r="N38" s="15"/>
-      <c r="O38" s="40"/>
-      <c r="P38" s="41"/>
-      <c r="Q38" s="41"/>
-      <c r="R38" s="42"/>
+      <c r="O38" s="41"/>
+      <c r="P38" s="42"/>
+      <c r="Q38" s="42"/>
+      <c r="R38" s="43"/>
     </row>
     <row r="39" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="18" t="str">
@@ -8843,10 +8843,10 @@
       </c>
       <c r="M39" s="13"/>
       <c r="N39" s="15"/>
-      <c r="O39" s="40"/>
-      <c r="P39" s="41"/>
-      <c r="Q39" s="41"/>
-      <c r="R39" s="42"/>
+      <c r="O39" s="41"/>
+      <c r="P39" s="42"/>
+      <c r="Q39" s="42"/>
+      <c r="R39" s="43"/>
     </row>
     <row r="40" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="18" t="str">
@@ -8863,10 +8863,10 @@
       </c>
       <c r="M40" s="13"/>
       <c r="N40" s="15"/>
-      <c r="O40" s="40"/>
-      <c r="P40" s="41"/>
-      <c r="Q40" s="41"/>
-      <c r="R40" s="42"/>
+      <c r="O40" s="41"/>
+      <c r="P40" s="42"/>
+      <c r="Q40" s="42"/>
+      <c r="R40" s="43"/>
     </row>
     <row r="41" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="18" t="str">
@@ -8883,10 +8883,10 @@
       </c>
       <c r="M41" s="13"/>
       <c r="N41" s="15"/>
-      <c r="O41" s="40"/>
-      <c r="P41" s="41"/>
-      <c r="Q41" s="41"/>
-      <c r="R41" s="42"/>
+      <c r="O41" s="41"/>
+      <c r="P41" s="42"/>
+      <c r="Q41" s="42"/>
+      <c r="R41" s="43"/>
     </row>
     <row r="42" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="18" t="str">
@@ -8903,10 +8903,10 @@
       </c>
       <c r="M42" s="13"/>
       <c r="N42" s="15"/>
-      <c r="O42" s="40"/>
-      <c r="P42" s="41"/>
-      <c r="Q42" s="41"/>
-      <c r="R42" s="42"/>
+      <c r="O42" s="41"/>
+      <c r="P42" s="42"/>
+      <c r="Q42" s="42"/>
+      <c r="R42" s="43"/>
     </row>
     <row r="43" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="18" t="str">
@@ -8923,10 +8923,10 @@
       </c>
       <c r="M43" s="13"/>
       <c r="N43" s="15"/>
-      <c r="O43" s="40"/>
-      <c r="P43" s="41"/>
-      <c r="Q43" s="41"/>
-      <c r="R43" s="42"/>
+      <c r="O43" s="41"/>
+      <c r="P43" s="42"/>
+      <c r="Q43" s="42"/>
+      <c r="R43" s="43"/>
     </row>
     <row r="44" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="18" t="str">
@@ -8943,10 +8943,10 @@
       </c>
       <c r="M44" s="13"/>
       <c r="N44" s="15"/>
-      <c r="O44" s="40"/>
-      <c r="P44" s="41"/>
-      <c r="Q44" s="41"/>
-      <c r="R44" s="42"/>
+      <c r="O44" s="41"/>
+      <c r="P44" s="42"/>
+      <c r="Q44" s="42"/>
+      <c r="R44" s="43"/>
     </row>
     <row r="45" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B45" s="18" t="str">
@@ -9776,32 +9776,32 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="C2:H2"/>
-    <mergeCell ref="M2:R2"/>
-    <mergeCell ref="M3:R3"/>
-    <mergeCell ref="M4:R22"/>
-    <mergeCell ref="J5:K14"/>
-    <mergeCell ref="M24:R24"/>
-    <mergeCell ref="M25:R25"/>
-    <mergeCell ref="O26:R26"/>
-    <mergeCell ref="O27:R27"/>
-    <mergeCell ref="O28:R28"/>
-    <mergeCell ref="O29:R29"/>
-    <mergeCell ref="O30:R30"/>
-    <mergeCell ref="O31:R31"/>
-    <mergeCell ref="O32:R32"/>
-    <mergeCell ref="O33:R33"/>
-    <mergeCell ref="O34:R34"/>
-    <mergeCell ref="O35:R35"/>
-    <mergeCell ref="O36:R36"/>
-    <mergeCell ref="O37:R37"/>
-    <mergeCell ref="O38:R38"/>
     <mergeCell ref="O44:R44"/>
     <mergeCell ref="O39:R39"/>
     <mergeCell ref="O40:R40"/>
     <mergeCell ref="O41:R41"/>
     <mergeCell ref="O42:R42"/>
     <mergeCell ref="O43:R43"/>
+    <mergeCell ref="O34:R34"/>
+    <mergeCell ref="O35:R35"/>
+    <mergeCell ref="O36:R36"/>
+    <mergeCell ref="O37:R37"/>
+    <mergeCell ref="O38:R38"/>
+    <mergeCell ref="O29:R29"/>
+    <mergeCell ref="O30:R30"/>
+    <mergeCell ref="O31:R31"/>
+    <mergeCell ref="O32:R32"/>
+    <mergeCell ref="O33:R33"/>
+    <mergeCell ref="M24:R24"/>
+    <mergeCell ref="M25:R25"/>
+    <mergeCell ref="O26:R26"/>
+    <mergeCell ref="O27:R27"/>
+    <mergeCell ref="O28:R28"/>
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="M2:R2"/>
+    <mergeCell ref="M3:R3"/>
+    <mergeCell ref="M4:R22"/>
+    <mergeCell ref="J5:K14"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B103">
     <cfRule type="expression" dxfId="7" priority="1">
@@ -9840,23 +9840,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="C2" s="35" t="s">
+      <c r="C2" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="D2" s="35"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
       <c r="L2" s="8"/>
-      <c r="M2" s="35" t="s">
+      <c r="M2" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="36"/>
-      <c r="O2" s="36"/>
-      <c r="P2" s="36"/>
-      <c r="Q2" s="36"/>
-      <c r="R2" s="36"/>
+      <c r="N2" s="23"/>
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
+      <c r="R2" s="23"/>
     </row>
     <row r="3" spans="2:18" ht="26.25" x14ac:dyDescent="0.4">
       <c r="G3" t="s">
@@ -9869,14 +9869,14 @@
         <f>SUM(Tabla113[Importa])</f>
         <v>2595.5</v>
       </c>
-      <c r="M3" s="38" t="s">
+      <c r="M3" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="38"/>
-      <c r="O3" s="38"/>
-      <c r="P3" s="38"/>
-      <c r="Q3" s="38"/>
-      <c r="R3" s="38"/>
+      <c r="N3" s="25"/>
+      <c r="O3" s="25"/>
+      <c r="P3" s="25"/>
+      <c r="Q3" s="25"/>
+      <c r="R3" s="25"/>
     </row>
     <row r="4" spans="2:18" ht="33.75" x14ac:dyDescent="0.5">
       <c r="B4" s="17" t="s">
@@ -9907,19 +9907,19 @@
         <f>COUNTIF(C5:C103,"&gt;0")</f>
         <v>19</v>
       </c>
-      <c r="M4" s="37" t="s">
+      <c r="M4" s="24" t="s">
         <v>128</v>
       </c>
-      <c r="N4" s="37"/>
-      <c r="O4" s="37"/>
-      <c r="P4" s="37"/>
-      <c r="Q4" s="37"/>
-      <c r="R4" s="37"/>
+      <c r="N4" s="24"/>
+      <c r="O4" s="24"/>
+      <c r="P4" s="24"/>
+      <c r="Q4" s="24"/>
+      <c r="R4" s="24"/>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B5" s="18">
         <f ca="1">IF(Tabla113[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C5">
         <f t="shared" ref="C5:C68" si="0">IF(ISNUMBER(E5), IF(ISNUMBER(C4), C4+1, 1), "")</f>
@@ -9941,21 +9941,21 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G5))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>63</v>
       </c>
-      <c r="J5" s="39" t="s">
+      <c r="J5" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="K5" s="39"/>
-      <c r="M5" s="37"/>
-      <c r="N5" s="37"/>
-      <c r="O5" s="37"/>
-      <c r="P5" s="37"/>
-      <c r="Q5" s="37"/>
-      <c r="R5" s="37"/>
+      <c r="K5" s="26"/>
+      <c r="M5" s="24"/>
+      <c r="N5" s="24"/>
+      <c r="O5" s="24"/>
+      <c r="P5" s="24"/>
+      <c r="Q5" s="24"/>
+      <c r="R5" s="24"/>
     </row>
     <row r="6" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C6">
         <f t="shared" si="0"/>
@@ -9977,19 +9977,19 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G6))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>58.5</v>
       </c>
-      <c r="J6" s="39"/>
-      <c r="K6" s="39"/>
-      <c r="M6" s="37"/>
-      <c r="N6" s="37"/>
-      <c r="O6" s="37"/>
-      <c r="P6" s="37"/>
-      <c r="Q6" s="37"/>
-      <c r="R6" s="37"/>
+      <c r="J6" s="26"/>
+      <c r="K6" s="26"/>
+      <c r="M6" s="24"/>
+      <c r="N6" s="24"/>
+      <c r="O6" s="24"/>
+      <c r="P6" s="24"/>
+      <c r="Q6" s="24"/>
+      <c r="R6" s="24"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B7" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
@@ -10008,19 +10008,19 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G7))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>56</v>
       </c>
-      <c r="J7" s="39"/>
-      <c r="K7" s="39"/>
-      <c r="M7" s="37"/>
-      <c r="N7" s="37"/>
-      <c r="O7" s="37"/>
-      <c r="P7" s="37"/>
-      <c r="Q7" s="37"/>
-      <c r="R7" s="37"/>
+      <c r="J7" s="26"/>
+      <c r="K7" s="26"/>
+      <c r="M7" s="24"/>
+      <c r="N7" s="24"/>
+      <c r="O7" s="24"/>
+      <c r="P7" s="24"/>
+      <c r="Q7" s="24"/>
+      <c r="R7" s="24"/>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B8" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C8">
         <f t="shared" si="0"/>
@@ -10039,19 +10039,19 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G8))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>380</v>
       </c>
-      <c r="J8" s="39"/>
-      <c r="K8" s="39"/>
-      <c r="M8" s="37"/>
-      <c r="N8" s="37"/>
-      <c r="O8" s="37"/>
-      <c r="P8" s="37"/>
-      <c r="Q8" s="37"/>
-      <c r="R8" s="37"/>
+      <c r="J8" s="26"/>
+      <c r="K8" s="26"/>
+      <c r="M8" s="24"/>
+      <c r="N8" s="24"/>
+      <c r="O8" s="24"/>
+      <c r="P8" s="24"/>
+      <c r="Q8" s="24"/>
+      <c r="R8" s="24"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B9" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C9">
         <f t="shared" si="0"/>
@@ -10070,19 +10070,19 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G9))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>142</v>
       </c>
-      <c r="J9" s="39"/>
-      <c r="K9" s="39"/>
-      <c r="M9" s="37"/>
-      <c r="N9" s="37"/>
-      <c r="O9" s="37"/>
-      <c r="P9" s="37"/>
-      <c r="Q9" s="37"/>
-      <c r="R9" s="37"/>
+      <c r="J9" s="26"/>
+      <c r="K9" s="26"/>
+      <c r="M9" s="24"/>
+      <c r="N9" s="24"/>
+      <c r="O9" s="24"/>
+      <c r="P9" s="24"/>
+      <c r="Q9" s="24"/>
+      <c r="R9" s="24"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B10" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C10">
         <f t="shared" si="0"/>
@@ -10104,19 +10104,19 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G10))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>36</v>
       </c>
-      <c r="J10" s="39"/>
-      <c r="K10" s="39"/>
-      <c r="M10" s="37"/>
-      <c r="N10" s="37"/>
-      <c r="O10" s="37"/>
-      <c r="P10" s="37"/>
-      <c r="Q10" s="37"/>
-      <c r="R10" s="37"/>
+      <c r="J10" s="26"/>
+      <c r="K10" s="26"/>
+      <c r="M10" s="24"/>
+      <c r="N10" s="24"/>
+      <c r="O10" s="24"/>
+      <c r="P10" s="24"/>
+      <c r="Q10" s="24"/>
+      <c r="R10" s="24"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B11" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C11">
         <f t="shared" si="0"/>
@@ -10138,19 +10138,19 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G11))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>27</v>
       </c>
-      <c r="J11" s="39"/>
-      <c r="K11" s="39"/>
-      <c r="M11" s="37"/>
-      <c r="N11" s="37"/>
-      <c r="O11" s="37"/>
-      <c r="P11" s="37"/>
-      <c r="Q11" s="37"/>
-      <c r="R11" s="37"/>
+      <c r="J11" s="26"/>
+      <c r="K11" s="26"/>
+      <c r="M11" s="24"/>
+      <c r="N11" s="24"/>
+      <c r="O11" s="24"/>
+      <c r="P11" s="24"/>
+      <c r="Q11" s="24"/>
+      <c r="R11" s="24"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B12" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C12">
         <f t="shared" si="0"/>
@@ -10169,19 +10169,19 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G12))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>126</v>
       </c>
-      <c r="J12" s="39"/>
-      <c r="K12" s="39"/>
-      <c r="M12" s="37"/>
-      <c r="N12" s="37"/>
-      <c r="O12" s="37"/>
-      <c r="P12" s="37"/>
-      <c r="Q12" s="37"/>
-      <c r="R12" s="37"/>
+      <c r="J12" s="26"/>
+      <c r="K12" s="26"/>
+      <c r="M12" s="24"/>
+      <c r="N12" s="24"/>
+      <c r="O12" s="24"/>
+      <c r="P12" s="24"/>
+      <c r="Q12" s="24"/>
+      <c r="R12" s="24"/>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B13" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C13">
         <f t="shared" si="0"/>
@@ -10200,19 +10200,19 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G13))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>15</v>
       </c>
-      <c r="J13" s="39"/>
-      <c r="K13" s="39"/>
-      <c r="M13" s="37"/>
-      <c r="N13" s="37"/>
-      <c r="O13" s="37"/>
-      <c r="P13" s="37"/>
-      <c r="Q13" s="37"/>
-      <c r="R13" s="37"/>
+      <c r="J13" s="26"/>
+      <c r="K13" s="26"/>
+      <c r="M13" s="24"/>
+      <c r="N13" s="24"/>
+      <c r="O13" s="24"/>
+      <c r="P13" s="24"/>
+      <c r="Q13" s="24"/>
+      <c r="R13" s="24"/>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B14" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C14">
         <f t="shared" si="0"/>
@@ -10234,19 +10234,19 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G14))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>81</v>
       </c>
-      <c r="J14" s="39"/>
-      <c r="K14" s="39"/>
-      <c r="M14" s="37"/>
-      <c r="N14" s="37"/>
-      <c r="O14" s="37"/>
-      <c r="P14" s="37"/>
-      <c r="Q14" s="37"/>
-      <c r="R14" s="37"/>
+      <c r="J14" s="26"/>
+      <c r="K14" s="26"/>
+      <c r="M14" s="24"/>
+      <c r="N14" s="24"/>
+      <c r="O14" s="24"/>
+      <c r="P14" s="24"/>
+      <c r="Q14" s="24"/>
+      <c r="R14" s="24"/>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B15" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C15">
         <f t="shared" si="0"/>
@@ -10268,17 +10268,17 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G15))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>64</v>
       </c>
-      <c r="M15" s="37"/>
-      <c r="N15" s="37"/>
-      <c r="O15" s="37"/>
-      <c r="P15" s="37"/>
-      <c r="Q15" s="37"/>
-      <c r="R15" s="37"/>
+      <c r="M15" s="24"/>
+      <c r="N15" s="24"/>
+      <c r="O15" s="24"/>
+      <c r="P15" s="24"/>
+      <c r="Q15" s="24"/>
+      <c r="R15" s="24"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B16" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C16">
         <f t="shared" si="0"/>
@@ -10297,17 +10297,17 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G16))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>160</v>
       </c>
-      <c r="M16" s="37"/>
-      <c r="N16" s="37"/>
-      <c r="O16" s="37"/>
-      <c r="P16" s="37"/>
-      <c r="Q16" s="37"/>
-      <c r="R16" s="37"/>
+      <c r="M16" s="24"/>
+      <c r="N16" s="24"/>
+      <c r="O16" s="24"/>
+      <c r="P16" s="24"/>
+      <c r="Q16" s="24"/>
+      <c r="R16" s="24"/>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B17" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C17">
         <f t="shared" si="0"/>
@@ -10326,17 +10326,17 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G17))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>280</v>
       </c>
-      <c r="M17" s="37"/>
-      <c r="N17" s="37"/>
-      <c r="O17" s="37"/>
-      <c r="P17" s="37"/>
-      <c r="Q17" s="37"/>
-      <c r="R17" s="37"/>
+      <c r="M17" s="24"/>
+      <c r="N17" s="24"/>
+      <c r="O17" s="24"/>
+      <c r="P17" s="24"/>
+      <c r="Q17" s="24"/>
+      <c r="R17" s="24"/>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B18" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C18">
         <f t="shared" si="0"/>
@@ -10355,17 +10355,17 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G18))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>650</v>
       </c>
-      <c r="M18" s="37"/>
-      <c r="N18" s="37"/>
-      <c r="O18" s="37"/>
-      <c r="P18" s="37"/>
-      <c r="Q18" s="37"/>
-      <c r="R18" s="37"/>
+      <c r="M18" s="24"/>
+      <c r="N18" s="24"/>
+      <c r="O18" s="24"/>
+      <c r="P18" s="24"/>
+      <c r="Q18" s="24"/>
+      <c r="R18" s="24"/>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B19" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C19">
         <f t="shared" si="0"/>
@@ -10384,17 +10384,17 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G19))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>280</v>
       </c>
-      <c r="M19" s="37"/>
-      <c r="N19" s="37"/>
-      <c r="O19" s="37"/>
-      <c r="P19" s="37"/>
-      <c r="Q19" s="37"/>
-      <c r="R19" s="37"/>
+      <c r="M19" s="24"/>
+      <c r="N19" s="24"/>
+      <c r="O19" s="24"/>
+      <c r="P19" s="24"/>
+      <c r="Q19" s="24"/>
+      <c r="R19" s="24"/>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B20" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C20">
         <f t="shared" si="0"/>
@@ -10413,12 +10413,12 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G20))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>45</v>
       </c>
-      <c r="M20" s="37"/>
-      <c r="N20" s="37"/>
-      <c r="O20" s="37"/>
-      <c r="P20" s="37"/>
-      <c r="Q20" s="37"/>
-      <c r="R20" s="37"/>
+      <c r="M20" s="24"/>
+      <c r="N20" s="24"/>
+      <c r="O20" s="24"/>
+      <c r="P20" s="24"/>
+      <c r="Q20" s="24"/>
+      <c r="R20" s="24"/>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B21" s="18" t="str">
@@ -10442,12 +10442,12 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G21))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>50</v>
       </c>
-      <c r="M21" s="37"/>
-      <c r="N21" s="37"/>
-      <c r="O21" s="37"/>
-      <c r="P21" s="37"/>
-      <c r="Q21" s="37"/>
-      <c r="R21" s="37"/>
+      <c r="M21" s="24"/>
+      <c r="N21" s="24"/>
+      <c r="O21" s="24"/>
+      <c r="P21" s="24"/>
+      <c r="Q21" s="24"/>
+      <c r="R21" s="24"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B22" s="18" t="str">
@@ -10471,12 +10471,12 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G22))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>42</v>
       </c>
-      <c r="M22" s="37"/>
-      <c r="N22" s="37"/>
-      <c r="O22" s="37"/>
-      <c r="P22" s="37"/>
-      <c r="Q22" s="37"/>
-      <c r="R22" s="37"/>
+      <c r="M22" s="24"/>
+      <c r="N22" s="24"/>
+      <c r="O22" s="24"/>
+      <c r="P22" s="24"/>
+      <c r="Q22" s="24"/>
+      <c r="R22" s="24"/>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B23" s="18" t="str">
@@ -10514,14 +10514,14 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G24))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M24" s="33" t="s">
+      <c r="M24" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="N24" s="46"/>
-      <c r="O24" s="46"/>
-      <c r="P24" s="46"/>
-      <c r="Q24" s="46"/>
-      <c r="R24" s="46"/>
+      <c r="N24" s="40"/>
+      <c r="O24" s="40"/>
+      <c r="P24" s="40"/>
+      <c r="Q24" s="40"/>
+      <c r="R24" s="40"/>
     </row>
     <row r="25" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="18" t="str">
@@ -10536,12 +10536,12 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G25))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M25" s="38"/>
-      <c r="N25" s="38"/>
-      <c r="O25" s="38"/>
-      <c r="P25" s="38"/>
-      <c r="Q25" s="38"/>
-      <c r="R25" s="38"/>
+      <c r="M25" s="25"/>
+      <c r="N25" s="25"/>
+      <c r="O25" s="25"/>
+      <c r="P25" s="25"/>
+      <c r="Q25" s="25"/>
+      <c r="R25" s="25"/>
     </row>
     <row r="26" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="18" t="str">
@@ -10562,12 +10562,12 @@
       <c r="N26" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="O26" s="32" t="s">
+      <c r="O26" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="P26" s="32"/>
-      <c r="Q26" s="32"/>
-      <c r="R26" s="32"/>
+      <c r="P26" s="39"/>
+      <c r="Q26" s="39"/>
+      <c r="R26" s="39"/>
     </row>
     <row r="27" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="18" t="str">
@@ -10588,12 +10588,12 @@
       <c r="N27" s="15">
         <v>80</v>
       </c>
-      <c r="O27" s="40" t="s">
+      <c r="O27" s="41" t="s">
         <v>94</v>
       </c>
-      <c r="P27" s="41"/>
-      <c r="Q27" s="41"/>
-      <c r="R27" s="42"/>
+      <c r="P27" s="42"/>
+      <c r="Q27" s="42"/>
+      <c r="R27" s="43"/>
     </row>
     <row r="28" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="18" t="str">
@@ -10614,12 +10614,12 @@
       <c r="N28" s="15">
         <v>160</v>
       </c>
-      <c r="O28" s="40" t="s">
+      <c r="O28" s="41" t="s">
         <v>95</v>
       </c>
-      <c r="P28" s="41"/>
-      <c r="Q28" s="41"/>
-      <c r="R28" s="42"/>
+      <c r="P28" s="42"/>
+      <c r="Q28" s="42"/>
+      <c r="R28" s="43"/>
     </row>
     <row r="29" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="18" t="str">
@@ -10640,12 +10640,12 @@
       <c r="N29" s="15">
         <v>2030</v>
       </c>
-      <c r="O29" s="40" t="s">
+      <c r="O29" s="41" t="s">
         <v>95</v>
       </c>
-      <c r="P29" s="41"/>
-      <c r="Q29" s="41"/>
-      <c r="R29" s="42"/>
+      <c r="P29" s="42"/>
+      <c r="Q29" s="42"/>
+      <c r="R29" s="43"/>
     </row>
     <row r="30" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="18" t="str">
@@ -10666,12 +10666,12 @@
       <c r="N30" s="15">
         <v>1492</v>
       </c>
-      <c r="O30" s="40" t="s">
+      <c r="O30" s="41" t="s">
         <v>95</v>
       </c>
-      <c r="P30" s="41"/>
-      <c r="Q30" s="41"/>
-      <c r="R30" s="42"/>
+      <c r="P30" s="42"/>
+      <c r="Q30" s="42"/>
+      <c r="R30" s="43"/>
     </row>
     <row r="31" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="18" t="str">
@@ -10692,12 +10692,12 @@
       <c r="N31" s="15">
         <v>1550</v>
       </c>
-      <c r="O31" s="40" t="s">
+      <c r="O31" s="41" t="s">
         <v>95</v>
       </c>
-      <c r="P31" s="41"/>
-      <c r="Q31" s="41"/>
-      <c r="R31" s="42"/>
+      <c r="P31" s="42"/>
+      <c r="Q31" s="42"/>
+      <c r="R31" s="43"/>
     </row>
     <row r="32" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="18" t="str">
@@ -10718,12 +10718,12 @@
       <c r="N32" s="15">
         <v>7781</v>
       </c>
-      <c r="O32" s="40" t="s">
+      <c r="O32" s="41" t="s">
         <v>126</v>
       </c>
-      <c r="P32" s="41"/>
-      <c r="Q32" s="41"/>
-      <c r="R32" s="42"/>
+      <c r="P32" s="42"/>
+      <c r="Q32" s="42"/>
+      <c r="R32" s="43"/>
     </row>
     <row r="33" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="18" t="str">
@@ -10744,12 +10744,12 @@
       <c r="N33" s="15">
         <v>69</v>
       </c>
-      <c r="O33" s="40" t="s">
+      <c r="O33" s="41" t="s">
         <v>100</v>
       </c>
-      <c r="P33" s="41"/>
-      <c r="Q33" s="41"/>
-      <c r="R33" s="42"/>
+      <c r="P33" s="42"/>
+      <c r="Q33" s="42"/>
+      <c r="R33" s="43"/>
     </row>
     <row r="34" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="18" t="str">
@@ -10770,12 +10770,12 @@
       <c r="N34" s="15">
         <v>1500</v>
       </c>
-      <c r="O34" s="40" t="s">
+      <c r="O34" s="41" t="s">
         <v>102</v>
       </c>
-      <c r="P34" s="41"/>
-      <c r="Q34" s="41"/>
-      <c r="R34" s="42"/>
+      <c r="P34" s="42"/>
+      <c r="Q34" s="42"/>
+      <c r="R34" s="43"/>
     </row>
     <row r="35" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="18" t="str">
@@ -10796,12 +10796,12 @@
       <c r="N35" s="15">
         <v>14662</v>
       </c>
-      <c r="O35" s="40" t="s">
+      <c r="O35" s="41" t="s">
         <v>103</v>
       </c>
-      <c r="P35" s="41"/>
-      <c r="Q35" s="41"/>
-      <c r="R35" s="42"/>
+      <c r="P35" s="42"/>
+      <c r="Q35" s="42"/>
+      <c r="R35" s="43"/>
     </row>
     <row r="36" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="18" t="str">
@@ -10818,10 +10818,10 @@
       </c>
       <c r="M36" s="13"/>
       <c r="N36" s="15"/>
-      <c r="O36" s="40"/>
-      <c r="P36" s="41"/>
-      <c r="Q36" s="41"/>
-      <c r="R36" s="42"/>
+      <c r="O36" s="41"/>
+      <c r="P36" s="42"/>
+      <c r="Q36" s="42"/>
+      <c r="R36" s="43"/>
     </row>
     <row r="37" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="18" t="str">
@@ -10838,10 +10838,10 @@
       </c>
       <c r="M37" s="13"/>
       <c r="N37" s="15"/>
-      <c r="O37" s="40"/>
-      <c r="P37" s="41"/>
-      <c r="Q37" s="41"/>
-      <c r="R37" s="42"/>
+      <c r="O37" s="41"/>
+      <c r="P37" s="42"/>
+      <c r="Q37" s="42"/>
+      <c r="R37" s="43"/>
     </row>
     <row r="38" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="18" t="str">
@@ -10858,10 +10858,10 @@
       </c>
       <c r="M38" s="13"/>
       <c r="N38" s="15"/>
-      <c r="O38" s="40"/>
-      <c r="P38" s="41"/>
-      <c r="Q38" s="41"/>
-      <c r="R38" s="42"/>
+      <c r="O38" s="41"/>
+      <c r="P38" s="42"/>
+      <c r="Q38" s="42"/>
+      <c r="R38" s="43"/>
     </row>
     <row r="39" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="18" t="str">
@@ -10878,10 +10878,10 @@
       </c>
       <c r="M39" s="13"/>
       <c r="N39" s="15"/>
-      <c r="O39" s="40"/>
-      <c r="P39" s="41"/>
-      <c r="Q39" s="41"/>
-      <c r="R39" s="42"/>
+      <c r="O39" s="41"/>
+      <c r="P39" s="42"/>
+      <c r="Q39" s="42"/>
+      <c r="R39" s="43"/>
     </row>
     <row r="40" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="18" t="str">
@@ -10898,10 +10898,10 @@
       </c>
       <c r="M40" s="13"/>
       <c r="N40" s="15"/>
-      <c r="O40" s="40"/>
-      <c r="P40" s="41"/>
-      <c r="Q40" s="41"/>
-      <c r="R40" s="42"/>
+      <c r="O40" s="41"/>
+      <c r="P40" s="42"/>
+      <c r="Q40" s="42"/>
+      <c r="R40" s="43"/>
     </row>
     <row r="41" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="18" t="str">
@@ -10918,10 +10918,10 @@
       </c>
       <c r="M41" s="13"/>
       <c r="N41" s="15"/>
-      <c r="O41" s="40"/>
-      <c r="P41" s="41"/>
-      <c r="Q41" s="41"/>
-      <c r="R41" s="42"/>
+      <c r="O41" s="41"/>
+      <c r="P41" s="42"/>
+      <c r="Q41" s="42"/>
+      <c r="R41" s="43"/>
     </row>
     <row r="42" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="18" t="str">
@@ -10938,10 +10938,10 @@
       </c>
       <c r="M42" s="13"/>
       <c r="N42" s="15"/>
-      <c r="O42" s="40"/>
-      <c r="P42" s="41"/>
-      <c r="Q42" s="41"/>
-      <c r="R42" s="42"/>
+      <c r="O42" s="41"/>
+      <c r="P42" s="42"/>
+      <c r="Q42" s="42"/>
+      <c r="R42" s="43"/>
     </row>
     <row r="43" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="18" t="str">
@@ -10958,10 +10958,10 @@
       </c>
       <c r="M43" s="13"/>
       <c r="N43" s="15"/>
-      <c r="O43" s="40"/>
-      <c r="P43" s="41"/>
-      <c r="Q43" s="41"/>
-      <c r="R43" s="42"/>
+      <c r="O43" s="41"/>
+      <c r="P43" s="42"/>
+      <c r="Q43" s="42"/>
+      <c r="R43" s="43"/>
     </row>
     <row r="44" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="18" t="str">
@@ -10978,10 +10978,10 @@
       </c>
       <c r="M44" s="13"/>
       <c r="N44" s="15"/>
-      <c r="O44" s="40"/>
-      <c r="P44" s="41"/>
-      <c r="Q44" s="41"/>
-      <c r="R44" s="42"/>
+      <c r="O44" s="41"/>
+      <c r="P44" s="42"/>
+      <c r="Q44" s="42"/>
+      <c r="R44" s="43"/>
     </row>
     <row r="45" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B45" s="18" t="str">
@@ -11811,32 +11811,32 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="C2:H2"/>
-    <mergeCell ref="M2:R2"/>
-    <mergeCell ref="M3:R3"/>
-    <mergeCell ref="M4:R22"/>
-    <mergeCell ref="J5:K14"/>
-    <mergeCell ref="M24:R24"/>
-    <mergeCell ref="M25:R25"/>
-    <mergeCell ref="O26:R26"/>
-    <mergeCell ref="O27:R27"/>
-    <mergeCell ref="O28:R28"/>
-    <mergeCell ref="O29:R29"/>
-    <mergeCell ref="O30:R30"/>
-    <mergeCell ref="O31:R31"/>
-    <mergeCell ref="O32:R32"/>
-    <mergeCell ref="O33:R33"/>
-    <mergeCell ref="O34:R34"/>
-    <mergeCell ref="O35:R35"/>
-    <mergeCell ref="O36:R36"/>
-    <mergeCell ref="O37:R37"/>
-    <mergeCell ref="O38:R38"/>
     <mergeCell ref="O44:R44"/>
     <mergeCell ref="O39:R39"/>
     <mergeCell ref="O40:R40"/>
     <mergeCell ref="O41:R41"/>
     <mergeCell ref="O42:R42"/>
     <mergeCell ref="O43:R43"/>
+    <mergeCell ref="O34:R34"/>
+    <mergeCell ref="O35:R35"/>
+    <mergeCell ref="O36:R36"/>
+    <mergeCell ref="O37:R37"/>
+    <mergeCell ref="O38:R38"/>
+    <mergeCell ref="O29:R29"/>
+    <mergeCell ref="O30:R30"/>
+    <mergeCell ref="O31:R31"/>
+    <mergeCell ref="O32:R32"/>
+    <mergeCell ref="O33:R33"/>
+    <mergeCell ref="M24:R24"/>
+    <mergeCell ref="M25:R25"/>
+    <mergeCell ref="O26:R26"/>
+    <mergeCell ref="O27:R27"/>
+    <mergeCell ref="O28:R28"/>
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="M2:R2"/>
+    <mergeCell ref="M3:R3"/>
+    <mergeCell ref="M4:R22"/>
+    <mergeCell ref="J5:K14"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B103">
     <cfRule type="expression" dxfId="5" priority="1">
@@ -11875,23 +11875,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="C2" s="35" t="s">
+      <c r="C2" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="D2" s="35"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
       <c r="L2" s="8"/>
-      <c r="M2" s="35" t="s">
+      <c r="M2" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="36"/>
-      <c r="O2" s="36"/>
-      <c r="P2" s="36"/>
-      <c r="Q2" s="36"/>
-      <c r="R2" s="36"/>
+      <c r="N2" s="23"/>
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
+      <c r="R2" s="23"/>
     </row>
     <row r="3" spans="2:18" ht="26.25" x14ac:dyDescent="0.4">
       <c r="G3" t="s">
@@ -11904,14 +11904,14 @@
         <f>SUM(Tabla114[Importa])</f>
         <v>4762.5</v>
       </c>
-      <c r="M3" s="38" t="s">
+      <c r="M3" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="38"/>
-      <c r="O3" s="38"/>
-      <c r="P3" s="38"/>
-      <c r="Q3" s="38"/>
-      <c r="R3" s="38"/>
+      <c r="N3" s="25"/>
+      <c r="O3" s="25"/>
+      <c r="P3" s="25"/>
+      <c r="Q3" s="25"/>
+      <c r="R3" s="25"/>
     </row>
     <row r="4" spans="2:18" ht="33.75" x14ac:dyDescent="0.5">
       <c r="B4" s="17" t="s">
@@ -11942,19 +11942,19 @@
         <f>COUNTIF(C5:C103,"&gt;0")</f>
         <v>23</v>
       </c>
-      <c r="M4" s="37" t="s">
+      <c r="M4" s="24" t="s">
         <v>151</v>
       </c>
-      <c r="N4" s="37"/>
-      <c r="O4" s="37"/>
-      <c r="P4" s="37"/>
-      <c r="Q4" s="37"/>
-      <c r="R4" s="37"/>
+      <c r="N4" s="24"/>
+      <c r="O4" s="24"/>
+      <c r="P4" s="24"/>
+      <c r="Q4" s="24"/>
+      <c r="R4" s="24"/>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B5" s="18">
         <f ca="1">IF(Tabla114[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C5">
         <f t="shared" ref="C5:C68" si="0">IF(ISNUMBER(E5), IF(ISNUMBER(C4), C4+1, 1), "")</f>
@@ -11973,21 +11973,21 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G5))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>60</v>
       </c>
-      <c r="J5" s="39" t="s">
+      <c r="J5" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="K5" s="39"/>
-      <c r="M5" s="37"/>
-      <c r="N5" s="37"/>
-      <c r="O5" s="37"/>
-      <c r="P5" s="37"/>
-      <c r="Q5" s="37"/>
-      <c r="R5" s="37"/>
+      <c r="K5" s="26"/>
+      <c r="M5" s="24"/>
+      <c r="N5" s="24"/>
+      <c r="O5" s="24"/>
+      <c r="P5" s="24"/>
+      <c r="Q5" s="24"/>
+      <c r="R5" s="24"/>
     </row>
     <row r="6" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C6">
         <f t="shared" si="0"/>
@@ -12006,19 +12006,19 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G6))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>60</v>
       </c>
-      <c r="J6" s="39"/>
-      <c r="K6" s="39"/>
-      <c r="M6" s="37"/>
-      <c r="N6" s="37"/>
-      <c r="O6" s="37"/>
-      <c r="P6" s="37"/>
-      <c r="Q6" s="37"/>
-      <c r="R6" s="37"/>
+      <c r="J6" s="26"/>
+      <c r="K6" s="26"/>
+      <c r="M6" s="24"/>
+      <c r="N6" s="24"/>
+      <c r="O6" s="24"/>
+      <c r="P6" s="24"/>
+      <c r="Q6" s="24"/>
+      <c r="R6" s="24"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B7" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
@@ -12037,19 +12037,19 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G7))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>65</v>
       </c>
-      <c r="J7" s="39"/>
-      <c r="K7" s="39"/>
-      <c r="M7" s="37"/>
-      <c r="N7" s="37"/>
-      <c r="O7" s="37"/>
-      <c r="P7" s="37"/>
-      <c r="Q7" s="37"/>
-      <c r="R7" s="37"/>
+      <c r="J7" s="26"/>
+      <c r="K7" s="26"/>
+      <c r="M7" s="24"/>
+      <c r="N7" s="24"/>
+      <c r="O7" s="24"/>
+      <c r="P7" s="24"/>
+      <c r="Q7" s="24"/>
+      <c r="R7" s="24"/>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B8" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C8">
         <f t="shared" si="0"/>
@@ -12071,19 +12071,19 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G8))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>90</v>
       </c>
-      <c r="J8" s="39"/>
-      <c r="K8" s="39"/>
-      <c r="M8" s="37"/>
-      <c r="N8" s="37"/>
-      <c r="O8" s="37"/>
-      <c r="P8" s="37"/>
-      <c r="Q8" s="37"/>
-      <c r="R8" s="37"/>
+      <c r="J8" s="26"/>
+      <c r="K8" s="26"/>
+      <c r="M8" s="24"/>
+      <c r="N8" s="24"/>
+      <c r="O8" s="24"/>
+      <c r="P8" s="24"/>
+      <c r="Q8" s="24"/>
+      <c r="R8" s="24"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B9" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C9">
         <f t="shared" si="0"/>
@@ -12105,19 +12105,19 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G9))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>252</v>
       </c>
-      <c r="J9" s="39"/>
-      <c r="K9" s="39"/>
-      <c r="M9" s="37"/>
-      <c r="N9" s="37"/>
-      <c r="O9" s="37"/>
-      <c r="P9" s="37"/>
-      <c r="Q9" s="37"/>
-      <c r="R9" s="37"/>
+      <c r="J9" s="26"/>
+      <c r="K9" s="26"/>
+      <c r="M9" s="24"/>
+      <c r="N9" s="24"/>
+      <c r="O9" s="24"/>
+      <c r="P9" s="24"/>
+      <c r="Q9" s="24"/>
+      <c r="R9" s="24"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B10" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C10">
         <f t="shared" si="0"/>
@@ -12139,19 +12139,19 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G10))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>171</v>
       </c>
-      <c r="J10" s="39"/>
-      <c r="K10" s="39"/>
-      <c r="M10" s="37"/>
-      <c r="N10" s="37"/>
-      <c r="O10" s="37"/>
-      <c r="P10" s="37"/>
-      <c r="Q10" s="37"/>
-      <c r="R10" s="37"/>
+      <c r="J10" s="26"/>
+      <c r="K10" s="26"/>
+      <c r="M10" s="24"/>
+      <c r="N10" s="24"/>
+      <c r="O10" s="24"/>
+      <c r="P10" s="24"/>
+      <c r="Q10" s="24"/>
+      <c r="R10" s="24"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B11" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C11">
         <f t="shared" si="0"/>
@@ -12173,19 +12173,19 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G11))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>108</v>
       </c>
-      <c r="J11" s="39"/>
-      <c r="K11" s="39"/>
-      <c r="M11" s="37"/>
-      <c r="N11" s="37"/>
-      <c r="O11" s="37"/>
-      <c r="P11" s="37"/>
-      <c r="Q11" s="37"/>
-      <c r="R11" s="37"/>
+      <c r="J11" s="26"/>
+      <c r="K11" s="26"/>
+      <c r="M11" s="24"/>
+      <c r="N11" s="24"/>
+      <c r="O11" s="24"/>
+      <c r="P11" s="24"/>
+      <c r="Q11" s="24"/>
+      <c r="R11" s="24"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B12" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C12">
         <f t="shared" si="0"/>
@@ -12207,19 +12207,19 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G12))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>111.5</v>
       </c>
-      <c r="J12" s="39"/>
-      <c r="K12" s="39"/>
-      <c r="M12" s="37"/>
-      <c r="N12" s="37"/>
-      <c r="O12" s="37"/>
-      <c r="P12" s="37"/>
-      <c r="Q12" s="37"/>
-      <c r="R12" s="37"/>
+      <c r="J12" s="26"/>
+      <c r="K12" s="26"/>
+      <c r="M12" s="24"/>
+      <c r="N12" s="24"/>
+      <c r="O12" s="24"/>
+      <c r="P12" s="24"/>
+      <c r="Q12" s="24"/>
+      <c r="R12" s="24"/>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B13" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C13">
         <f t="shared" si="0"/>
@@ -12241,19 +12241,19 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G13))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>45</v>
       </c>
-      <c r="J13" s="39"/>
-      <c r="K13" s="39"/>
-      <c r="M13" s="37"/>
-      <c r="N13" s="37"/>
-      <c r="O13" s="37"/>
-      <c r="P13" s="37"/>
-      <c r="Q13" s="37"/>
-      <c r="R13" s="37"/>
+      <c r="J13" s="26"/>
+      <c r="K13" s="26"/>
+      <c r="M13" s="24"/>
+      <c r="N13" s="24"/>
+      <c r="O13" s="24"/>
+      <c r="P13" s="24"/>
+      <c r="Q13" s="24"/>
+      <c r="R13" s="24"/>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B14" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C14">
         <f t="shared" si="0"/>
@@ -12275,19 +12275,19 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G14))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>31.5</v>
       </c>
-      <c r="J14" s="39"/>
-      <c r="K14" s="39"/>
-      <c r="M14" s="37"/>
-      <c r="N14" s="37"/>
-      <c r="O14" s="37"/>
-      <c r="P14" s="37"/>
-      <c r="Q14" s="37"/>
-      <c r="R14" s="37"/>
+      <c r="J14" s="26"/>
+      <c r="K14" s="26"/>
+      <c r="M14" s="24"/>
+      <c r="N14" s="24"/>
+      <c r="O14" s="24"/>
+      <c r="P14" s="24"/>
+      <c r="Q14" s="24"/>
+      <c r="R14" s="24"/>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B15" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C15">
         <f t="shared" si="0"/>
@@ -12309,17 +12309,17 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G15))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>315</v>
       </c>
-      <c r="M15" s="37"/>
-      <c r="N15" s="37"/>
-      <c r="O15" s="37"/>
-      <c r="P15" s="37"/>
-      <c r="Q15" s="37"/>
-      <c r="R15" s="37"/>
+      <c r="M15" s="24"/>
+      <c r="N15" s="24"/>
+      <c r="O15" s="24"/>
+      <c r="P15" s="24"/>
+      <c r="Q15" s="24"/>
+      <c r="R15" s="24"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B16" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C16">
         <f t="shared" si="0"/>
@@ -12341,17 +12341,17 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G16))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>532</v>
       </c>
-      <c r="M16" s="37"/>
-      <c r="N16" s="37"/>
-      <c r="O16" s="37"/>
-      <c r="P16" s="37"/>
-      <c r="Q16" s="37"/>
-      <c r="R16" s="37"/>
+      <c r="M16" s="24"/>
+      <c r="N16" s="24"/>
+      <c r="O16" s="24"/>
+      <c r="P16" s="24"/>
+      <c r="Q16" s="24"/>
+      <c r="R16" s="24"/>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B17" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C17">
         <f t="shared" si="0"/>
@@ -12373,17 +12373,17 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G17))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>27</v>
       </c>
-      <c r="M17" s="37"/>
-      <c r="N17" s="37"/>
-      <c r="O17" s="37"/>
-      <c r="P17" s="37"/>
-      <c r="Q17" s="37"/>
-      <c r="R17" s="37"/>
+      <c r="M17" s="24"/>
+      <c r="N17" s="24"/>
+      <c r="O17" s="24"/>
+      <c r="P17" s="24"/>
+      <c r="Q17" s="24"/>
+      <c r="R17" s="24"/>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B18" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C18">
         <f t="shared" si="0"/>
@@ -12405,17 +12405,17 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G18))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>274.5</v>
       </c>
-      <c r="M18" s="37"/>
-      <c r="N18" s="37"/>
-      <c r="O18" s="37"/>
-      <c r="P18" s="37"/>
-      <c r="Q18" s="37"/>
-      <c r="R18" s="37"/>
+      <c r="M18" s="24"/>
+      <c r="N18" s="24"/>
+      <c r="O18" s="24"/>
+      <c r="P18" s="24"/>
+      <c r="Q18" s="24"/>
+      <c r="R18" s="24"/>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B19" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C19">
         <f t="shared" si="0"/>
@@ -12437,17 +12437,17 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G19))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>135</v>
       </c>
-      <c r="M19" s="37"/>
-      <c r="N19" s="37"/>
-      <c r="O19" s="37"/>
-      <c r="P19" s="37"/>
-      <c r="Q19" s="37"/>
-      <c r="R19" s="37"/>
+      <c r="M19" s="24"/>
+      <c r="N19" s="24"/>
+      <c r="O19" s="24"/>
+      <c r="P19" s="24"/>
+      <c r="Q19" s="24"/>
+      <c r="R19" s="24"/>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B20" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C20">
         <f t="shared" si="0"/>
@@ -12466,12 +12466,12 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G20))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>690</v>
       </c>
-      <c r="M20" s="37"/>
-      <c r="N20" s="37"/>
-      <c r="O20" s="37"/>
-      <c r="P20" s="37"/>
-      <c r="Q20" s="37"/>
-      <c r="R20" s="37"/>
+      <c r="M20" s="24"/>
+      <c r="N20" s="24"/>
+      <c r="O20" s="24"/>
+      <c r="P20" s="24"/>
+      <c r="Q20" s="24"/>
+      <c r="R20" s="24"/>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B21" s="18" t="str">
@@ -12498,12 +12498,12 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G21))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>36</v>
       </c>
-      <c r="M21" s="37"/>
-      <c r="N21" s="37"/>
-      <c r="O21" s="37"/>
-      <c r="P21" s="37"/>
-      <c r="Q21" s="37"/>
-      <c r="R21" s="37"/>
+      <c r="M21" s="24"/>
+      <c r="N21" s="24"/>
+      <c r="O21" s="24"/>
+      <c r="P21" s="24"/>
+      <c r="Q21" s="24"/>
+      <c r="R21" s="24"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B22" s="18" t="str">
@@ -12530,12 +12530,12 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G22))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>117</v>
       </c>
-      <c r="M22" s="37"/>
-      <c r="N22" s="37"/>
-      <c r="O22" s="37"/>
-      <c r="P22" s="37"/>
-      <c r="Q22" s="37"/>
-      <c r="R22" s="37"/>
+      <c r="M22" s="24"/>
+      <c r="N22" s="24"/>
+      <c r="O22" s="24"/>
+      <c r="P22" s="24"/>
+      <c r="Q22" s="24"/>
+      <c r="R22" s="24"/>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B23" s="18" t="str">
@@ -12585,14 +12585,14 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G24))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>150</v>
       </c>
-      <c r="M24" s="33" t="s">
+      <c r="M24" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="N24" s="46"/>
-      <c r="O24" s="46"/>
-      <c r="P24" s="46"/>
-      <c r="Q24" s="46"/>
-      <c r="R24" s="46"/>
+      <c r="N24" s="40"/>
+      <c r="O24" s="40"/>
+      <c r="P24" s="40"/>
+      <c r="Q24" s="40"/>
+      <c r="R24" s="40"/>
     </row>
     <row r="25" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="18" t="str">
@@ -12616,12 +12616,12 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G25))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>50</v>
       </c>
-      <c r="M25" s="38"/>
-      <c r="N25" s="38"/>
-      <c r="O25" s="38"/>
-      <c r="P25" s="38"/>
-      <c r="Q25" s="38"/>
-      <c r="R25" s="38"/>
+      <c r="M25" s="25"/>
+      <c r="N25" s="25"/>
+      <c r="O25" s="25"/>
+      <c r="P25" s="25"/>
+      <c r="Q25" s="25"/>
+      <c r="R25" s="25"/>
     </row>
     <row r="26" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="18" t="str">
@@ -12651,12 +12651,12 @@
       <c r="N26" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="O26" s="32" t="s">
+      <c r="O26" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="P26" s="32"/>
-      <c r="Q26" s="32"/>
-      <c r="R26" s="32"/>
+      <c r="P26" s="39"/>
+      <c r="Q26" s="39"/>
+      <c r="R26" s="39"/>
     </row>
     <row r="27" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="18" t="str">
@@ -12686,10 +12686,10 @@
       <c r="N27" s="15">
         <v>9985</v>
       </c>
-      <c r="O27" s="40"/>
-      <c r="P27" s="41"/>
-      <c r="Q27" s="41"/>
-      <c r="R27" s="42"/>
+      <c r="O27" s="41"/>
+      <c r="P27" s="42"/>
+      <c r="Q27" s="42"/>
+      <c r="R27" s="43"/>
     </row>
     <row r="28" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="18" t="str">
@@ -12709,10 +12709,10 @@
       </c>
       <c r="M28" s="13"/>
       <c r="N28" s="15"/>
-      <c r="O28" s="40"/>
-      <c r="P28" s="41"/>
-      <c r="Q28" s="41"/>
-      <c r="R28" s="42"/>
+      <c r="O28" s="41"/>
+      <c r="P28" s="42"/>
+      <c r="Q28" s="42"/>
+      <c r="R28" s="43"/>
     </row>
     <row r="29" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="18" t="str">
@@ -12729,10 +12729,10 @@
       </c>
       <c r="M29" s="13"/>
       <c r="N29" s="15"/>
-      <c r="O29" s="40"/>
-      <c r="P29" s="41"/>
-      <c r="Q29" s="41"/>
-      <c r="R29" s="42"/>
+      <c r="O29" s="41"/>
+      <c r="P29" s="42"/>
+      <c r="Q29" s="42"/>
+      <c r="R29" s="43"/>
     </row>
     <row r="30" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="18" t="str">
@@ -12749,10 +12749,10 @@
       </c>
       <c r="M30" s="13"/>
       <c r="N30" s="15"/>
-      <c r="O30" s="40"/>
-      <c r="P30" s="41"/>
-      <c r="Q30" s="41"/>
-      <c r="R30" s="42"/>
+      <c r="O30" s="41"/>
+      <c r="P30" s="42"/>
+      <c r="Q30" s="42"/>
+      <c r="R30" s="43"/>
     </row>
     <row r="31" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="18" t="str">
@@ -12769,10 +12769,10 @@
       </c>
       <c r="M31" s="13"/>
       <c r="N31" s="15"/>
-      <c r="O31" s="40"/>
-      <c r="P31" s="41"/>
-      <c r="Q31" s="41"/>
-      <c r="R31" s="42"/>
+      <c r="O31" s="41"/>
+      <c r="P31" s="42"/>
+      <c r="Q31" s="42"/>
+      <c r="R31" s="43"/>
     </row>
     <row r="32" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="18" t="str">
@@ -12789,10 +12789,10 @@
       </c>
       <c r="M32" s="13"/>
       <c r="N32" s="15"/>
-      <c r="O32" s="40"/>
-      <c r="P32" s="41"/>
-      <c r="Q32" s="41"/>
-      <c r="R32" s="42"/>
+      <c r="O32" s="41"/>
+      <c r="P32" s="42"/>
+      <c r="Q32" s="42"/>
+      <c r="R32" s="43"/>
     </row>
     <row r="33" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="18" t="str">
@@ -12809,10 +12809,10 @@
       </c>
       <c r="M33" s="13"/>
       <c r="N33" s="15"/>
-      <c r="O33" s="40"/>
-      <c r="P33" s="41"/>
-      <c r="Q33" s="41"/>
-      <c r="R33" s="42"/>
+      <c r="O33" s="41"/>
+      <c r="P33" s="42"/>
+      <c r="Q33" s="42"/>
+      <c r="R33" s="43"/>
     </row>
     <row r="34" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="18" t="str">
@@ -12829,10 +12829,10 @@
       </c>
       <c r="M34" s="13"/>
       <c r="N34" s="15"/>
-      <c r="O34" s="40"/>
-      <c r="P34" s="41"/>
-      <c r="Q34" s="41"/>
-      <c r="R34" s="42"/>
+      <c r="O34" s="41"/>
+      <c r="P34" s="42"/>
+      <c r="Q34" s="42"/>
+      <c r="R34" s="43"/>
     </row>
     <row r="35" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="18" t="str">
@@ -12849,10 +12849,10 @@
       </c>
       <c r="M35" s="13"/>
       <c r="N35" s="15"/>
-      <c r="O35" s="40"/>
-      <c r="P35" s="41"/>
-      <c r="Q35" s="41"/>
-      <c r="R35" s="42"/>
+      <c r="O35" s="41"/>
+      <c r="P35" s="42"/>
+      <c r="Q35" s="42"/>
+      <c r="R35" s="43"/>
     </row>
     <row r="36" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="18" t="str">
@@ -12869,10 +12869,10 @@
       </c>
       <c r="M36" s="13"/>
       <c r="N36" s="15"/>
-      <c r="O36" s="40"/>
-      <c r="P36" s="41"/>
-      <c r="Q36" s="41"/>
-      <c r="R36" s="42"/>
+      <c r="O36" s="41"/>
+      <c r="P36" s="42"/>
+      <c r="Q36" s="42"/>
+      <c r="R36" s="43"/>
     </row>
     <row r="37" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="18" t="str">
@@ -12889,10 +12889,10 @@
       </c>
       <c r="M37" s="13"/>
       <c r="N37" s="15"/>
-      <c r="O37" s="40"/>
-      <c r="P37" s="41"/>
-      <c r="Q37" s="41"/>
-      <c r="R37" s="42"/>
+      <c r="O37" s="41"/>
+      <c r="P37" s="42"/>
+      <c r="Q37" s="42"/>
+      <c r="R37" s="43"/>
     </row>
     <row r="38" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="18" t="str">
@@ -12909,10 +12909,10 @@
       </c>
       <c r="M38" s="13"/>
       <c r="N38" s="15"/>
-      <c r="O38" s="40"/>
-      <c r="P38" s="41"/>
-      <c r="Q38" s="41"/>
-      <c r="R38" s="42"/>
+      <c r="O38" s="41"/>
+      <c r="P38" s="42"/>
+      <c r="Q38" s="42"/>
+      <c r="R38" s="43"/>
     </row>
     <row r="39" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="18" t="str">
@@ -12929,10 +12929,10 @@
       </c>
       <c r="M39" s="13"/>
       <c r="N39" s="15"/>
-      <c r="O39" s="40"/>
-      <c r="P39" s="41"/>
-      <c r="Q39" s="41"/>
-      <c r="R39" s="42"/>
+      <c r="O39" s="41"/>
+      <c r="P39" s="42"/>
+      <c r="Q39" s="42"/>
+      <c r="R39" s="43"/>
     </row>
     <row r="40" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="18" t="str">
@@ -12949,10 +12949,10 @@
       </c>
       <c r="M40" s="13"/>
       <c r="N40" s="15"/>
-      <c r="O40" s="40"/>
-      <c r="P40" s="41"/>
-      <c r="Q40" s="41"/>
-      <c r="R40" s="42"/>
+      <c r="O40" s="41"/>
+      <c r="P40" s="42"/>
+      <c r="Q40" s="42"/>
+      <c r="R40" s="43"/>
     </row>
     <row r="41" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="18" t="str">
@@ -12969,10 +12969,10 @@
       </c>
       <c r="M41" s="13"/>
       <c r="N41" s="15"/>
-      <c r="O41" s="40"/>
-      <c r="P41" s="41"/>
-      <c r="Q41" s="41"/>
-      <c r="R41" s="42"/>
+      <c r="O41" s="41"/>
+      <c r="P41" s="42"/>
+      <c r="Q41" s="42"/>
+      <c r="R41" s="43"/>
     </row>
     <row r="42" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="18" t="str">
@@ -12989,10 +12989,10 @@
       </c>
       <c r="M42" s="13"/>
       <c r="N42" s="15"/>
-      <c r="O42" s="40"/>
-      <c r="P42" s="41"/>
-      <c r="Q42" s="41"/>
-      <c r="R42" s="42"/>
+      <c r="O42" s="41"/>
+      <c r="P42" s="42"/>
+      <c r="Q42" s="42"/>
+      <c r="R42" s="43"/>
     </row>
     <row r="43" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="18" t="str">
@@ -13009,10 +13009,10 @@
       </c>
       <c r="M43" s="13"/>
       <c r="N43" s="15"/>
-      <c r="O43" s="40"/>
-      <c r="P43" s="41"/>
-      <c r="Q43" s="41"/>
-      <c r="R43" s="42"/>
+      <c r="O43" s="41"/>
+      <c r="P43" s="42"/>
+      <c r="Q43" s="42"/>
+      <c r="R43" s="43"/>
     </row>
     <row r="44" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="18" t="str">
@@ -13029,10 +13029,10 @@
       </c>
       <c r="M44" s="13"/>
       <c r="N44" s="15"/>
-      <c r="O44" s="40"/>
-      <c r="P44" s="41"/>
-      <c r="Q44" s="41"/>
-      <c r="R44" s="42"/>
+      <c r="O44" s="41"/>
+      <c r="P44" s="42"/>
+      <c r="Q44" s="42"/>
+      <c r="R44" s="43"/>
     </row>
     <row r="45" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B45" s="18" t="str">
@@ -13862,32 +13862,32 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="C2:H2"/>
-    <mergeCell ref="M2:R2"/>
-    <mergeCell ref="M3:R3"/>
-    <mergeCell ref="M4:R22"/>
-    <mergeCell ref="J5:K14"/>
-    <mergeCell ref="M24:R24"/>
-    <mergeCell ref="M25:R25"/>
-    <mergeCell ref="O26:R26"/>
-    <mergeCell ref="O27:R27"/>
-    <mergeCell ref="O28:R28"/>
-    <mergeCell ref="O29:R29"/>
-    <mergeCell ref="O30:R30"/>
-    <mergeCell ref="O31:R31"/>
-    <mergeCell ref="O32:R32"/>
-    <mergeCell ref="O33:R33"/>
-    <mergeCell ref="O34:R34"/>
-    <mergeCell ref="O35:R35"/>
-    <mergeCell ref="O36:R36"/>
-    <mergeCell ref="O37:R37"/>
-    <mergeCell ref="O38:R38"/>
     <mergeCell ref="O44:R44"/>
     <mergeCell ref="O39:R39"/>
     <mergeCell ref="O40:R40"/>
     <mergeCell ref="O41:R41"/>
     <mergeCell ref="O42:R42"/>
     <mergeCell ref="O43:R43"/>
+    <mergeCell ref="O34:R34"/>
+    <mergeCell ref="O35:R35"/>
+    <mergeCell ref="O36:R36"/>
+    <mergeCell ref="O37:R37"/>
+    <mergeCell ref="O38:R38"/>
+    <mergeCell ref="O29:R29"/>
+    <mergeCell ref="O30:R30"/>
+    <mergeCell ref="O31:R31"/>
+    <mergeCell ref="O32:R32"/>
+    <mergeCell ref="O33:R33"/>
+    <mergeCell ref="M24:R24"/>
+    <mergeCell ref="M25:R25"/>
+    <mergeCell ref="O26:R26"/>
+    <mergeCell ref="O27:R27"/>
+    <mergeCell ref="O28:R28"/>
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="M2:R2"/>
+    <mergeCell ref="M3:R3"/>
+    <mergeCell ref="M4:R22"/>
+    <mergeCell ref="J5:K14"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B103">
     <cfRule type="expression" dxfId="3" priority="1">
@@ -13925,23 +13925,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="C2" s="35" t="s">
+      <c r="C2" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="35"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
       <c r="L2" s="8"/>
-      <c r="M2" s="35" t="s">
+      <c r="M2" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="36"/>
-      <c r="O2" s="36"/>
-      <c r="P2" s="36"/>
-      <c r="Q2" s="36"/>
-      <c r="R2" s="36"/>
+      <c r="N2" s="23"/>
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
+      <c r="R2" s="23"/>
     </row>
     <row r="3" spans="2:18" ht="26.25" x14ac:dyDescent="0.4">
       <c r="G3" t="s">
@@ -13954,14 +13954,14 @@
         <f>SUM(Tabla115[Importa])</f>
         <v>0</v>
       </c>
-      <c r="M3" s="38" t="s">
+      <c r="M3" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="38"/>
-      <c r="O3" s="38"/>
-      <c r="P3" s="38"/>
-      <c r="Q3" s="38"/>
-      <c r="R3" s="38"/>
+      <c r="N3" s="25"/>
+      <c r="O3" s="25"/>
+      <c r="P3" s="25"/>
+      <c r="Q3" s="25"/>
+      <c r="R3" s="25"/>
     </row>
     <row r="4" spans="2:18" ht="33.75" x14ac:dyDescent="0.5">
       <c r="B4" s="17" t="s">
@@ -13992,12 +13992,12 @@
         <f>COUNTIF(C5:C103,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="M4" s="37"/>
-      <c r="N4" s="37"/>
-      <c r="O4" s="37"/>
-      <c r="P4" s="37"/>
-      <c r="Q4" s="37"/>
-      <c r="R4" s="37"/>
+      <c r="M4" s="24"/>
+      <c r="N4" s="24"/>
+      <c r="O4" s="24"/>
+      <c r="P4" s="24"/>
+      <c r="Q4" s="24"/>
+      <c r="R4" s="24"/>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B5" s="18" t="str">
@@ -14012,21 +14012,21 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G5))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="J5" s="39" t="s">
+      <c r="J5" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="K5" s="39"/>
-      <c r="M5" s="37"/>
-      <c r="N5" s="37"/>
-      <c r="O5" s="37"/>
-      <c r="P5" s="37"/>
-      <c r="Q5" s="37"/>
-      <c r="R5" s="37"/>
+      <c r="K5" s="26"/>
+      <c r="M5" s="24"/>
+      <c r="N5" s="24"/>
+      <c r="O5" s="24"/>
+      <c r="P5" s="24"/>
+      <c r="Q5" s="24"/>
+      <c r="R5" s="24"/>
     </row>
     <row r="6" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C6" t="str">
         <f t="shared" si="0"/>
@@ -14036,19 +14036,19 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G6))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="J6" s="39"/>
-      <c r="K6" s="39"/>
-      <c r="M6" s="37"/>
-      <c r="N6" s="37"/>
-      <c r="O6" s="37"/>
-      <c r="P6" s="37"/>
-      <c r="Q6" s="37"/>
-      <c r="R6" s="37"/>
+      <c r="J6" s="26"/>
+      <c r="K6" s="26"/>
+      <c r="M6" s="24"/>
+      <c r="N6" s="24"/>
+      <c r="O6" s="24"/>
+      <c r="P6" s="24"/>
+      <c r="Q6" s="24"/>
+      <c r="R6" s="24"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B7" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C7" t="str">
         <f t="shared" si="0"/>
@@ -14058,19 +14058,19 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G7))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="J7" s="39"/>
-      <c r="K7" s="39"/>
-      <c r="M7" s="37"/>
-      <c r="N7" s="37"/>
-      <c r="O7" s="37"/>
-      <c r="P7" s="37"/>
-      <c r="Q7" s="37"/>
-      <c r="R7" s="37"/>
+      <c r="J7" s="26"/>
+      <c r="K7" s="26"/>
+      <c r="M7" s="24"/>
+      <c r="N7" s="24"/>
+      <c r="O7" s="24"/>
+      <c r="P7" s="24"/>
+      <c r="Q7" s="24"/>
+      <c r="R7" s="24"/>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B8" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C8" t="str">
         <f t="shared" si="0"/>
@@ -14080,19 +14080,19 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G8))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="J8" s="39"/>
-      <c r="K8" s="39"/>
-      <c r="M8" s="37"/>
-      <c r="N8" s="37"/>
-      <c r="O8" s="37"/>
-      <c r="P8" s="37"/>
-      <c r="Q8" s="37"/>
-      <c r="R8" s="37"/>
+      <c r="J8" s="26"/>
+      <c r="K8" s="26"/>
+      <c r="M8" s="24"/>
+      <c r="N8" s="24"/>
+      <c r="O8" s="24"/>
+      <c r="P8" s="24"/>
+      <c r="Q8" s="24"/>
+      <c r="R8" s="24"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B9" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C9" t="str">
         <f t="shared" si="0"/>
@@ -14102,19 +14102,19 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G9))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="J9" s="39"/>
-      <c r="K9" s="39"/>
-      <c r="M9" s="37"/>
-      <c r="N9" s="37"/>
-      <c r="O9" s="37"/>
-      <c r="P9" s="37"/>
-      <c r="Q9" s="37"/>
-      <c r="R9" s="37"/>
+      <c r="J9" s="26"/>
+      <c r="K9" s="26"/>
+      <c r="M9" s="24"/>
+      <c r="N9" s="24"/>
+      <c r="O9" s="24"/>
+      <c r="P9" s="24"/>
+      <c r="Q9" s="24"/>
+      <c r="R9" s="24"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B10" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C10" t="str">
         <f t="shared" si="0"/>
@@ -14124,19 +14124,19 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G10))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="J10" s="39"/>
-      <c r="K10" s="39"/>
-      <c r="M10" s="37"/>
-      <c r="N10" s="37"/>
-      <c r="O10" s="37"/>
-      <c r="P10" s="37"/>
-      <c r="Q10" s="37"/>
-      <c r="R10" s="37"/>
+      <c r="J10" s="26"/>
+      <c r="K10" s="26"/>
+      <c r="M10" s="24"/>
+      <c r="N10" s="24"/>
+      <c r="O10" s="24"/>
+      <c r="P10" s="24"/>
+      <c r="Q10" s="24"/>
+      <c r="R10" s="24"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B11" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C11" t="str">
         <f t="shared" si="0"/>
@@ -14146,19 +14146,19 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G11))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="J11" s="39"/>
-      <c r="K11" s="39"/>
-      <c r="M11" s="37"/>
-      <c r="N11" s="37"/>
-      <c r="O11" s="37"/>
-      <c r="P11" s="37"/>
-      <c r="Q11" s="37"/>
-      <c r="R11" s="37"/>
+      <c r="J11" s="26"/>
+      <c r="K11" s="26"/>
+      <c r="M11" s="24"/>
+      <c r="N11" s="24"/>
+      <c r="O11" s="24"/>
+      <c r="P11" s="24"/>
+      <c r="Q11" s="24"/>
+      <c r="R11" s="24"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B12" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C12" t="str">
         <f t="shared" si="0"/>
@@ -14168,19 +14168,19 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G12))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="J12" s="39"/>
-      <c r="K12" s="39"/>
-      <c r="M12" s="37"/>
-      <c r="N12" s="37"/>
-      <c r="O12" s="37"/>
-      <c r="P12" s="37"/>
-      <c r="Q12" s="37"/>
-      <c r="R12" s="37"/>
+      <c r="J12" s="26"/>
+      <c r="K12" s="26"/>
+      <c r="M12" s="24"/>
+      <c r="N12" s="24"/>
+      <c r="O12" s="24"/>
+      <c r="P12" s="24"/>
+      <c r="Q12" s="24"/>
+      <c r="R12" s="24"/>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B13" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C13" t="str">
         <f t="shared" si="0"/>
@@ -14190,19 +14190,19 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G13))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="J13" s="39"/>
-      <c r="K13" s="39"/>
-      <c r="M13" s="37"/>
-      <c r="N13" s="37"/>
-      <c r="O13" s="37"/>
-      <c r="P13" s="37"/>
-      <c r="Q13" s="37"/>
-      <c r="R13" s="37"/>
+      <c r="J13" s="26"/>
+      <c r="K13" s="26"/>
+      <c r="M13" s="24"/>
+      <c r="N13" s="24"/>
+      <c r="O13" s="24"/>
+      <c r="P13" s="24"/>
+      <c r="Q13" s="24"/>
+      <c r="R13" s="24"/>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B14" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C14" t="str">
         <f t="shared" si="0"/>
@@ -14212,19 +14212,19 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G14))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="J14" s="39"/>
-      <c r="K14" s="39"/>
-      <c r="M14" s="37"/>
-      <c r="N14" s="37"/>
-      <c r="O14" s="37"/>
-      <c r="P14" s="37"/>
-      <c r="Q14" s="37"/>
-      <c r="R14" s="37"/>
+      <c r="J14" s="26"/>
+      <c r="K14" s="26"/>
+      <c r="M14" s="24"/>
+      <c r="N14" s="24"/>
+      <c r="O14" s="24"/>
+      <c r="P14" s="24"/>
+      <c r="Q14" s="24"/>
+      <c r="R14" s="24"/>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B15" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C15" t="str">
         <f t="shared" si="0"/>
@@ -14234,17 +14234,17 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G15))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M15" s="37"/>
-      <c r="N15" s="37"/>
-      <c r="O15" s="37"/>
-      <c r="P15" s="37"/>
-      <c r="Q15" s="37"/>
-      <c r="R15" s="37"/>
+      <c r="M15" s="24"/>
+      <c r="N15" s="24"/>
+      <c r="O15" s="24"/>
+      <c r="P15" s="24"/>
+      <c r="Q15" s="24"/>
+      <c r="R15" s="24"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B16" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C16" t="str">
         <f t="shared" si="0"/>
@@ -14254,17 +14254,17 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G16))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M16" s="37"/>
-      <c r="N16" s="37"/>
-      <c r="O16" s="37"/>
-      <c r="P16" s="37"/>
-      <c r="Q16" s="37"/>
-      <c r="R16" s="37"/>
+      <c r="M16" s="24"/>
+      <c r="N16" s="24"/>
+      <c r="O16" s="24"/>
+      <c r="P16" s="24"/>
+      <c r="Q16" s="24"/>
+      <c r="R16" s="24"/>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B17" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C17" t="str">
         <f t="shared" si="0"/>
@@ -14274,17 +14274,17 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G17))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M17" s="37"/>
-      <c r="N17" s="37"/>
-      <c r="O17" s="37"/>
-      <c r="P17" s="37"/>
-      <c r="Q17" s="37"/>
-      <c r="R17" s="37"/>
+      <c r="M17" s="24"/>
+      <c r="N17" s="24"/>
+      <c r="O17" s="24"/>
+      <c r="P17" s="24"/>
+      <c r="Q17" s="24"/>
+      <c r="R17" s="24"/>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B18" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C18" t="str">
         <f t="shared" si="0"/>
@@ -14294,17 +14294,17 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G18))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M18" s="37"/>
-      <c r="N18" s="37"/>
-      <c r="O18" s="37"/>
-      <c r="P18" s="37"/>
-      <c r="Q18" s="37"/>
-      <c r="R18" s="37"/>
+      <c r="M18" s="24"/>
+      <c r="N18" s="24"/>
+      <c r="O18" s="24"/>
+      <c r="P18" s="24"/>
+      <c r="Q18" s="24"/>
+      <c r="R18" s="24"/>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B19" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C19" t="str">
         <f t="shared" si="0"/>
@@ -14314,17 +14314,17 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G19))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M19" s="37"/>
-      <c r="N19" s="37"/>
-      <c r="O19" s="37"/>
-      <c r="P19" s="37"/>
-      <c r="Q19" s="37"/>
-      <c r="R19" s="37"/>
+      <c r="M19" s="24"/>
+      <c r="N19" s="24"/>
+      <c r="O19" s="24"/>
+      <c r="P19" s="24"/>
+      <c r="Q19" s="24"/>
+      <c r="R19" s="24"/>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B20" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46102.810187962961</v>
+        <v>46106.442314467589</v>
       </c>
       <c r="C20" t="str">
         <f t="shared" si="0"/>
@@ -14334,12 +14334,12 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G20))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M20" s="37"/>
-      <c r="N20" s="37"/>
-      <c r="O20" s="37"/>
-      <c r="P20" s="37"/>
-      <c r="Q20" s="37"/>
-      <c r="R20" s="37"/>
+      <c r="M20" s="24"/>
+      <c r="N20" s="24"/>
+      <c r="O20" s="24"/>
+      <c r="P20" s="24"/>
+      <c r="Q20" s="24"/>
+      <c r="R20" s="24"/>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B21" s="18" t="str">
@@ -14354,12 +14354,12 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G21))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M21" s="37"/>
-      <c r="N21" s="37"/>
-      <c r="O21" s="37"/>
-      <c r="P21" s="37"/>
-      <c r="Q21" s="37"/>
-      <c r="R21" s="37"/>
+      <c r="M21" s="24"/>
+      <c r="N21" s="24"/>
+      <c r="O21" s="24"/>
+      <c r="P21" s="24"/>
+      <c r="Q21" s="24"/>
+      <c r="R21" s="24"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B22" s="18" t="str">
@@ -14374,12 +14374,12 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G22))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M22" s="37"/>
-      <c r="N22" s="37"/>
-      <c r="O22" s="37"/>
-      <c r="P22" s="37"/>
-      <c r="Q22" s="37"/>
-      <c r="R22" s="37"/>
+      <c r="M22" s="24"/>
+      <c r="N22" s="24"/>
+      <c r="O22" s="24"/>
+      <c r="P22" s="24"/>
+      <c r="Q22" s="24"/>
+      <c r="R22" s="24"/>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B23" s="18" t="str">
@@ -14408,14 +14408,14 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G24))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M24" s="33" t="s">
+      <c r="M24" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="N24" s="46"/>
-      <c r="O24" s="46"/>
-      <c r="P24" s="46"/>
-      <c r="Q24" s="46"/>
-      <c r="R24" s="46"/>
+      <c r="N24" s="40"/>
+      <c r="O24" s="40"/>
+      <c r="P24" s="40"/>
+      <c r="Q24" s="40"/>
+      <c r="R24" s="40"/>
     </row>
     <row r="25" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="18" t="str">
@@ -14430,12 +14430,12 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G25))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M25" s="38"/>
-      <c r="N25" s="38"/>
-      <c r="O25" s="38"/>
-      <c r="P25" s="38"/>
-      <c r="Q25" s="38"/>
-      <c r="R25" s="38"/>
+      <c r="M25" s="25"/>
+      <c r="N25" s="25"/>
+      <c r="O25" s="25"/>
+      <c r="P25" s="25"/>
+      <c r="Q25" s="25"/>
+      <c r="R25" s="25"/>
     </row>
     <row r="26" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="18" t="str">
@@ -14456,12 +14456,12 @@
       <c r="N26" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="O26" s="32" t="s">
+      <c r="O26" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="P26" s="32"/>
-      <c r="Q26" s="32"/>
-      <c r="R26" s="32"/>
+      <c r="P26" s="39"/>
+      <c r="Q26" s="39"/>
+      <c r="R26" s="39"/>
     </row>
     <row r="27" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="18" t="str">
@@ -14478,10 +14478,10 @@
       </c>
       <c r="M27" s="13"/>
       <c r="N27" s="15"/>
-      <c r="O27" s="40"/>
-      <c r="P27" s="41"/>
-      <c r="Q27" s="41"/>
-      <c r="R27" s="42"/>
+      <c r="O27" s="41"/>
+      <c r="P27" s="42"/>
+      <c r="Q27" s="42"/>
+      <c r="R27" s="43"/>
     </row>
     <row r="28" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="18" t="str">
@@ -14498,10 +14498,10 @@
       </c>
       <c r="M28" s="13"/>
       <c r="N28" s="15"/>
-      <c r="O28" s="40"/>
-      <c r="P28" s="41"/>
-      <c r="Q28" s="41"/>
-      <c r="R28" s="42"/>
+      <c r="O28" s="41"/>
+      <c r="P28" s="42"/>
+      <c r="Q28" s="42"/>
+      <c r="R28" s="43"/>
     </row>
     <row r="29" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="18" t="str">
@@ -14518,10 +14518,10 @@
       </c>
       <c r="M29" s="13"/>
       <c r="N29" s="15"/>
-      <c r="O29" s="40"/>
-      <c r="P29" s="41"/>
-      <c r="Q29" s="41"/>
-      <c r="R29" s="42"/>
+      <c r="O29" s="41"/>
+      <c r="P29" s="42"/>
+      <c r="Q29" s="42"/>
+      <c r="R29" s="43"/>
     </row>
     <row r="30" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="18" t="str">
@@ -14538,10 +14538,10 @@
       </c>
       <c r="M30" s="13"/>
       <c r="N30" s="15"/>
-      <c r="O30" s="40"/>
-      <c r="P30" s="41"/>
-      <c r="Q30" s="41"/>
-      <c r="R30" s="42"/>
+      <c r="O30" s="41"/>
+      <c r="P30" s="42"/>
+      <c r="Q30" s="42"/>
+      <c r="R30" s="43"/>
     </row>
     <row r="31" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="18" t="str">
@@ -14558,10 +14558,10 @@
       </c>
       <c r="M31" s="13"/>
       <c r="N31" s="15"/>
-      <c r="O31" s="40"/>
-      <c r="P31" s="41"/>
-      <c r="Q31" s="41"/>
-      <c r="R31" s="42"/>
+      <c r="O31" s="41"/>
+      <c r="P31" s="42"/>
+      <c r="Q31" s="42"/>
+      <c r="R31" s="43"/>
     </row>
     <row r="32" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="18" t="str">
@@ -14578,10 +14578,10 @@
       </c>
       <c r="M32" s="13"/>
       <c r="N32" s="15"/>
-      <c r="O32" s="40"/>
-      <c r="P32" s="41"/>
-      <c r="Q32" s="41"/>
-      <c r="R32" s="42"/>
+      <c r="O32" s="41"/>
+      <c r="P32" s="42"/>
+      <c r="Q32" s="42"/>
+      <c r="R32" s="43"/>
     </row>
     <row r="33" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="18" t="str">
@@ -14598,10 +14598,10 @@
       </c>
       <c r="M33" s="13"/>
       <c r="N33" s="15"/>
-      <c r="O33" s="40"/>
-      <c r="P33" s="41"/>
-      <c r="Q33" s="41"/>
-      <c r="R33" s="42"/>
+      <c r="O33" s="41"/>
+      <c r="P33" s="42"/>
+      <c r="Q33" s="42"/>
+      <c r="R33" s="43"/>
     </row>
     <row r="34" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="18" t="str">
@@ -14618,10 +14618,10 @@
       </c>
       <c r="M34" s="13"/>
       <c r="N34" s="15"/>
-      <c r="O34" s="40"/>
-      <c r="P34" s="41"/>
-      <c r="Q34" s="41"/>
-      <c r="R34" s="42"/>
+      <c r="O34" s="41"/>
+      <c r="P34" s="42"/>
+      <c r="Q34" s="42"/>
+      <c r="R34" s="43"/>
     </row>
     <row r="35" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="18" t="str">
@@ -14638,10 +14638,10 @@
       </c>
       <c r="M35" s="13"/>
       <c r="N35" s="15"/>
-      <c r="O35" s="40"/>
-      <c r="P35" s="41"/>
-      <c r="Q35" s="41"/>
-      <c r="R35" s="42"/>
+      <c r="O35" s="41"/>
+      <c r="P35" s="42"/>
+      <c r="Q35" s="42"/>
+      <c r="R35" s="43"/>
     </row>
     <row r="36" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="18" t="str">
@@ -14658,10 +14658,10 @@
       </c>
       <c r="M36" s="13"/>
       <c r="N36" s="15"/>
-      <c r="O36" s="40"/>
-      <c r="P36" s="41"/>
-      <c r="Q36" s="41"/>
-      <c r="R36" s="42"/>
+      <c r="O36" s="41"/>
+      <c r="P36" s="42"/>
+      <c r="Q36" s="42"/>
+      <c r="R36" s="43"/>
     </row>
     <row r="37" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="18" t="str">
@@ -14678,10 +14678,10 @@
       </c>
       <c r="M37" s="13"/>
       <c r="N37" s="15"/>
-      <c r="O37" s="40"/>
-      <c r="P37" s="41"/>
-      <c r="Q37" s="41"/>
-      <c r="R37" s="42"/>
+      <c r="O37" s="41"/>
+      <c r="P37" s="42"/>
+      <c r="Q37" s="42"/>
+      <c r="R37" s="43"/>
     </row>
     <row r="38" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="18" t="str">
@@ -14698,10 +14698,10 @@
       </c>
       <c r="M38" s="13"/>
       <c r="N38" s="15"/>
-      <c r="O38" s="40"/>
-      <c r="P38" s="41"/>
-      <c r="Q38" s="41"/>
-      <c r="R38" s="42"/>
+      <c r="O38" s="41"/>
+      <c r="P38" s="42"/>
+      <c r="Q38" s="42"/>
+      <c r="R38" s="43"/>
     </row>
     <row r="39" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="18" t="str">
@@ -14718,10 +14718,10 @@
       </c>
       <c r="M39" s="13"/>
       <c r="N39" s="15"/>
-      <c r="O39" s="40"/>
-      <c r="P39" s="41"/>
-      <c r="Q39" s="41"/>
-      <c r="R39" s="42"/>
+      <c r="O39" s="41"/>
+      <c r="P39" s="42"/>
+      <c r="Q39" s="42"/>
+      <c r="R39" s="43"/>
     </row>
     <row r="40" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="18" t="str">
@@ -14738,10 +14738,10 @@
       </c>
       <c r="M40" s="13"/>
       <c r="N40" s="15"/>
-      <c r="O40" s="40"/>
-      <c r="P40" s="41"/>
-      <c r="Q40" s="41"/>
-      <c r="R40" s="42"/>
+      <c r="O40" s="41"/>
+      <c r="P40" s="42"/>
+      <c r="Q40" s="42"/>
+      <c r="R40" s="43"/>
     </row>
     <row r="41" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="18" t="str">
@@ -14758,10 +14758,10 @@
       </c>
       <c r="M41" s="13"/>
       <c r="N41" s="15"/>
-      <c r="O41" s="40"/>
-      <c r="P41" s="41"/>
-      <c r="Q41" s="41"/>
-      <c r="R41" s="42"/>
+      <c r="O41" s="41"/>
+      <c r="P41" s="42"/>
+      <c r="Q41" s="42"/>
+      <c r="R41" s="43"/>
     </row>
     <row r="42" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="18" t="str">
@@ -14778,10 +14778,10 @@
       </c>
       <c r="M42" s="13"/>
       <c r="N42" s="15"/>
-      <c r="O42" s="40"/>
-      <c r="P42" s="41"/>
-      <c r="Q42" s="41"/>
-      <c r="R42" s="42"/>
+      <c r="O42" s="41"/>
+      <c r="P42" s="42"/>
+      <c r="Q42" s="42"/>
+      <c r="R42" s="43"/>
     </row>
     <row r="43" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="18" t="str">
@@ -14798,10 +14798,10 @@
       </c>
       <c r="M43" s="13"/>
       <c r="N43" s="15"/>
-      <c r="O43" s="40"/>
-      <c r="P43" s="41"/>
-      <c r="Q43" s="41"/>
-      <c r="R43" s="42"/>
+      <c r="O43" s="41"/>
+      <c r="P43" s="42"/>
+      <c r="Q43" s="42"/>
+      <c r="R43" s="43"/>
     </row>
     <row r="44" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="18" t="str">
@@ -14818,10 +14818,10 @@
       </c>
       <c r="M44" s="13"/>
       <c r="N44" s="15"/>
-      <c r="O44" s="40"/>
-      <c r="P44" s="41"/>
-      <c r="Q44" s="41"/>
-      <c r="R44" s="42"/>
+      <c r="O44" s="41"/>
+      <c r="P44" s="42"/>
+      <c r="Q44" s="42"/>
+      <c r="R44" s="43"/>
     </row>
     <row r="45" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B45" s="18" t="str">
@@ -15651,32 +15651,32 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="C2:H2"/>
-    <mergeCell ref="M2:R2"/>
-    <mergeCell ref="M3:R3"/>
-    <mergeCell ref="M4:R22"/>
-    <mergeCell ref="J5:K14"/>
-    <mergeCell ref="M24:R24"/>
-    <mergeCell ref="M25:R25"/>
-    <mergeCell ref="O26:R26"/>
-    <mergeCell ref="O27:R27"/>
-    <mergeCell ref="O28:R28"/>
-    <mergeCell ref="O29:R29"/>
-    <mergeCell ref="O30:R30"/>
-    <mergeCell ref="O31:R31"/>
-    <mergeCell ref="O32:R32"/>
-    <mergeCell ref="O33:R33"/>
-    <mergeCell ref="O34:R34"/>
-    <mergeCell ref="O35:R35"/>
-    <mergeCell ref="O36:R36"/>
-    <mergeCell ref="O37:R37"/>
-    <mergeCell ref="O38:R38"/>
     <mergeCell ref="O44:R44"/>
     <mergeCell ref="O39:R39"/>
     <mergeCell ref="O40:R40"/>
     <mergeCell ref="O41:R41"/>
     <mergeCell ref="O42:R42"/>
     <mergeCell ref="O43:R43"/>
+    <mergeCell ref="O34:R34"/>
+    <mergeCell ref="O35:R35"/>
+    <mergeCell ref="O36:R36"/>
+    <mergeCell ref="O37:R37"/>
+    <mergeCell ref="O38:R38"/>
+    <mergeCell ref="O29:R29"/>
+    <mergeCell ref="O30:R30"/>
+    <mergeCell ref="O31:R31"/>
+    <mergeCell ref="O32:R32"/>
+    <mergeCell ref="O33:R33"/>
+    <mergeCell ref="M24:R24"/>
+    <mergeCell ref="M25:R25"/>
+    <mergeCell ref="O26:R26"/>
+    <mergeCell ref="O27:R27"/>
+    <mergeCell ref="O28:R28"/>
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="M2:R2"/>
+    <mergeCell ref="M3:R3"/>
+    <mergeCell ref="M4:R22"/>
+    <mergeCell ref="J5:K14"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B103">
     <cfRule type="expression" dxfId="1" priority="1">
